--- a/research/traditional_assets/database/data/germany/germany_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_paper_forest_products.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07460628441596914</v>
+        <v>0.07441396556272123</v>
       </c>
       <c r="C2">
-        <v>27.00594782945159</v>
+        <v>26.8092815451279</v>
       </c>
       <c r="D2">
-        <v>15.20594782945158</v>
+        <v>15.2880815451279</v>
       </c>
       <c r="E2">
-        <v>-3.879999999999999</v>
+        <v>-3.6012</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2788</v>
       </c>
       <c r="G2">
         <v>11.8</v>
@@ -1451,28 +1451,28 @@
         <v>2.42</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01402364</v>
       </c>
       <c r="N2">
-        <v>2.42</v>
+        <v>2.40597636</v>
       </c>
       <c r="O2">
-        <v>0.726</v>
+        <v>0.721792908</v>
       </c>
       <c r="P2">
-        <v>1.694</v>
+        <v>1.684183452</v>
       </c>
       <c r="Q2">
-        <v>4.104</v>
+        <v>4.094183452</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07460628441596914</v>
+        <v>0.07480996521486993</v>
       </c>
       <c r="T2">
-        <v>0.6652721574126822</v>
+        <v>0.6699761019600445</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>172.5657532566438</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07441396556272123</v>
+        <v>0.07422164670947333</v>
       </c>
       <c r="C3">
-        <v>26.8092815451279</v>
+        <v>26.61350735683237</v>
       </c>
       <c r="D3">
-        <v>15.2880815451279</v>
+        <v>15.37110735683237</v>
       </c>
       <c r="E3">
-        <v>-3.6012</v>
+        <v>-3.3224</v>
       </c>
       <c r="F3">
-        <v>0.2788</v>
+        <v>0.5576</v>
       </c>
       <c r="G3">
         <v>11.8</v>
@@ -1533,28 +1533,28 @@
         <v>2.42</v>
       </c>
       <c r="M3">
-        <v>0.01402364</v>
+        <v>0.02804728</v>
       </c>
       <c r="N3">
-        <v>2.40597636</v>
+        <v>2.39195272</v>
       </c>
       <c r="O3">
-        <v>0.721792908</v>
+        <v>0.7175858159999999</v>
       </c>
       <c r="P3">
-        <v>1.684183452</v>
+        <v>1.674366904</v>
       </c>
       <c r="Q3">
-        <v>4.094183452</v>
+        <v>4.084366904</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07480996521486993</v>
+        <v>0.0750178027647687</v>
       </c>
       <c r="T3">
-        <v>0.6699761019600445</v>
+        <v>0.6747760453757204</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>172.5657532566438</v>
+        <v>86.2828766283219</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07422164670947333</v>
+        <v>0.07402932785622542</v>
       </c>
       <c r="C4">
-        <v>26.61350735683237</v>
+        <v>26.41863987819054</v>
       </c>
       <c r="D4">
-        <v>15.37110735683237</v>
+        <v>15.45503987819054</v>
       </c>
       <c r="E4">
-        <v>-3.3224</v>
+        <v>-3.0436</v>
       </c>
       <c r="F4">
-        <v>0.5576</v>
+        <v>0.8363999999999999</v>
       </c>
       <c r="G4">
         <v>11.8</v>
@@ -1615,28 +1615,28 @@
         <v>2.42</v>
       </c>
       <c r="M4">
-        <v>0.02804728</v>
+        <v>0.04207091999999999</v>
       </c>
       <c r="N4">
-        <v>2.39195272</v>
+        <v>2.37792908</v>
       </c>
       <c r="O4">
-        <v>0.7175858159999999</v>
+        <v>0.7133787239999999</v>
       </c>
       <c r="P4">
-        <v>1.674366904</v>
+        <v>1.664550356</v>
       </c>
       <c r="Q4">
-        <v>4.084366904</v>
+        <v>4.074550356</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0750178027647687</v>
+        <v>0.07522992562497466</v>
       </c>
       <c r="T4">
-        <v>0.6747760453757204</v>
+        <v>0.6796749566968743</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>86.2828766283219</v>
+        <v>57.52191775221461</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07402932785622542</v>
+        <v>0.0738370090029775</v>
       </c>
       <c r="C5">
-        <v>26.41863987819054</v>
+        <v>26.22469404376582</v>
       </c>
       <c r="D5">
-        <v>15.45503987819054</v>
+        <v>15.53989404376582</v>
       </c>
       <c r="E5">
-        <v>-3.0436</v>
+        <v>-2.764799999999999</v>
       </c>
       <c r="F5">
-        <v>0.8363999999999999</v>
+        <v>1.1152</v>
       </c>
       <c r="G5">
         <v>11.8</v>
@@ -1697,28 +1697,28 @@
         <v>2.42</v>
       </c>
       <c r="M5">
-        <v>0.04207091999999999</v>
+        <v>0.05609455999999999</v>
       </c>
       <c r="N5">
-        <v>2.37792908</v>
+        <v>2.36390544</v>
       </c>
       <c r="O5">
-        <v>0.7133787239999999</v>
+        <v>0.709171632</v>
       </c>
       <c r="P5">
-        <v>1.664550356</v>
+        <v>1.654733808</v>
       </c>
       <c r="Q5">
-        <v>4.074550356</v>
+        <v>4.064733808</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07522992562497466</v>
+        <v>0.0754464677114349</v>
       </c>
       <c r="T5">
-        <v>0.6796749566968743</v>
+        <v>0.684675928670552</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>57.52191775221461</v>
+        <v>43.14143831416095</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0738370090029775</v>
+        <v>0.07364469014972959</v>
       </c>
       <c r="C6">
-        <v>26.22469404376582</v>
+        <v>26.03168511791854</v>
       </c>
       <c r="D6">
-        <v>15.53989404376582</v>
+        <v>15.62568511791854</v>
       </c>
       <c r="E6">
-        <v>-2.764799999999999</v>
+        <v>-2.485999999999999</v>
       </c>
       <c r="F6">
-        <v>1.1152</v>
+        <v>1.394</v>
       </c>
       <c r="G6">
         <v>11.8</v>
@@ -1779,28 +1779,28 @@
         <v>2.42</v>
       </c>
       <c r="M6">
-        <v>0.05609455999999999</v>
+        <v>0.07011820000000001</v>
       </c>
       <c r="N6">
-        <v>2.36390544</v>
+        <v>2.3498818</v>
       </c>
       <c r="O6">
-        <v>0.709171632</v>
+        <v>0.70496454</v>
       </c>
       <c r="P6">
-        <v>1.654733808</v>
+        <v>1.64491726</v>
       </c>
       <c r="Q6">
-        <v>4.064733808</v>
+        <v>4.05491726</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0754464677114349</v>
+        <v>0.07566756857866273</v>
       </c>
       <c r="T6">
-        <v>0.684675928670552</v>
+        <v>0.6897821842647283</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>43.14143831416095</v>
+        <v>34.51315065132875</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07364469014972959</v>
+        <v>0.07345237129648169</v>
       </c>
       <c r="C7">
-        <v>26.03168511791854</v>
+        <v>25.83962870396001</v>
       </c>
       <c r="D7">
-        <v>15.62568511791854</v>
+        <v>15.71242870396</v>
       </c>
       <c r="E7">
-        <v>-2.485999999999999</v>
+        <v>-2.207199999999999</v>
       </c>
       <c r="F7">
-        <v>1.394</v>
+        <v>1.6728</v>
       </c>
       <c r="G7">
         <v>11.8</v>
@@ -1861,28 +1861,28 @@
         <v>2.42</v>
       </c>
       <c r="M7">
-        <v>0.07011820000000001</v>
+        <v>0.08414184</v>
       </c>
       <c r="N7">
-        <v>2.3498818</v>
+        <v>2.33585816</v>
       </c>
       <c r="O7">
-        <v>0.70496454</v>
+        <v>0.7007574479999999</v>
       </c>
       <c r="P7">
-        <v>1.64491726</v>
+        <v>1.635100712</v>
       </c>
       <c r="Q7">
-        <v>4.05491726</v>
+        <v>4.045100712</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07566756857866273</v>
+        <v>0.07589337371966137</v>
       </c>
       <c r="T7">
-        <v>0.6897821842647283</v>
+        <v>0.6949970835949509</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.51315065132875</v>
+        <v>28.7609588761073</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07345237129648169</v>
+        <v>0.07326005244323379</v>
       </c>
       <c r="C8">
-        <v>25.83962870396001</v>
+        <v>25.64854075361322</v>
       </c>
       <c r="D8">
-        <v>15.71242870396</v>
+        <v>15.80014075361321</v>
       </c>
       <c r="E8">
-        <v>-2.207199999999999</v>
+        <v>-1.9284</v>
       </c>
       <c r="F8">
-        <v>1.6728</v>
+        <v>1.9516</v>
       </c>
       <c r="G8">
         <v>11.8</v>
@@ -1943,28 +1943,28 @@
         <v>2.42</v>
       </c>
       <c r="M8">
-        <v>0.08414183999999998</v>
+        <v>0.09816547999999999</v>
       </c>
       <c r="N8">
-        <v>2.33585816</v>
+        <v>2.32183452</v>
       </c>
       <c r="O8">
-        <v>0.7007574479999999</v>
+        <v>0.6965503559999999</v>
       </c>
       <c r="P8">
-        <v>1.635100712</v>
+        <v>1.625284164</v>
       </c>
       <c r="Q8">
-        <v>4.045100712</v>
+        <v>4.035284164</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07589337371966137</v>
+        <v>0.07612403488519762</v>
       </c>
       <c r="T8">
-        <v>0.6949970835949509</v>
+        <v>0.7003241312978665</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.7609588761073</v>
+        <v>24.65225046523483</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07326005244323378</v>
+        <v>0.07306773358998589</v>
       </c>
       <c r="C9">
-        <v>25.64854075361322</v>
+        <v>25.45843757679219</v>
       </c>
       <c r="D9">
-        <v>15.80014075361322</v>
+        <v>15.88883757679219</v>
       </c>
       <c r="E9">
-        <v>-1.928399999999999</v>
+        <v>-1.6496</v>
       </c>
       <c r="F9">
-        <v>1.9516</v>
+        <v>2.2304</v>
       </c>
       <c r="G9">
         <v>11.8</v>
@@ -2025,28 +2025,28 @@
         <v>2.42</v>
       </c>
       <c r="M9">
-        <v>0.09816548</v>
+        <v>0.11218912</v>
       </c>
       <c r="N9">
-        <v>2.32183452</v>
+        <v>2.30781088</v>
       </c>
       <c r="O9">
-        <v>0.6965503559999999</v>
+        <v>0.6923432639999999</v>
       </c>
       <c r="P9">
-        <v>1.625284164</v>
+        <v>1.615467616</v>
       </c>
       <c r="Q9">
-        <v>4.035284164</v>
+        <v>4.025467616</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07612403488519762</v>
+        <v>0.07635971042389771</v>
       </c>
       <c r="T9">
-        <v>0.7003241312978665</v>
+        <v>0.7057669843856281</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.65225046523483</v>
+        <v>21.57071915708048</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07306773358998589</v>
+        <v>0.07287541473673798</v>
       </c>
       <c r="C10">
-        <v>25.45843757679219</v>
+        <v>25.26933585171257</v>
       </c>
       <c r="D10">
-        <v>15.88883757679219</v>
+        <v>15.97853585171257</v>
       </c>
       <c r="E10">
-        <v>-1.6496</v>
+        <v>-1.3708</v>
       </c>
       <c r="F10">
-        <v>2.2304</v>
+        <v>2.5092</v>
       </c>
       <c r="G10">
         <v>11.8</v>
@@ -2107,28 +2107,28 @@
         <v>2.42</v>
       </c>
       <c r="M10">
-        <v>0.11218912</v>
+        <v>0.12621276</v>
       </c>
       <c r="N10">
-        <v>2.30781088</v>
+        <v>2.29378724</v>
       </c>
       <c r="O10">
-        <v>0.6923432639999999</v>
+        <v>0.688136172</v>
       </c>
       <c r="P10">
-        <v>1.615467616</v>
+        <v>1.605651068</v>
       </c>
       <c r="Q10">
-        <v>4.025467616</v>
+        <v>4.015651068</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07635971042389771</v>
+        <v>0.076600565644767</v>
       </c>
       <c r="T10">
-        <v>0.7057669843856281</v>
+        <v>0.7113294606181756</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.57071915708048</v>
+        <v>19.17397258407154</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07287541473673798</v>
+        <v>0.07268309588349006</v>
       </c>
       <c r="C11">
-        <v>25.26933585171257</v>
+        <v>25.08125263534662</v>
       </c>
       <c r="D11">
-        <v>15.97853585171257</v>
+        <v>16.06925263534662</v>
       </c>
       <c r="E11">
-        <v>-1.3708</v>
+        <v>-1.092</v>
       </c>
       <c r="F11">
-        <v>2.5092</v>
+        <v>2.788</v>
       </c>
       <c r="G11">
         <v>11.8</v>
@@ -2189,28 +2189,28 @@
         <v>2.42</v>
       </c>
       <c r="M11">
-        <v>0.12621276</v>
+        <v>0.1402364</v>
       </c>
       <c r="N11">
-        <v>2.29378724</v>
+        <v>2.2797636</v>
       </c>
       <c r="O11">
-        <v>0.688136172</v>
+        <v>0.68392908</v>
       </c>
       <c r="P11">
-        <v>1.605651068</v>
+        <v>1.59583452</v>
       </c>
       <c r="Q11">
-        <v>4.015651068</v>
+        <v>4.005834520000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.076600565644767</v>
+        <v>0.07684677320387785</v>
       </c>
       <c r="T11">
-        <v>0.7113294606181756</v>
+        <v>0.7170155474336686</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.17397258407154</v>
+        <v>17.25657532566438</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07268309588349006</v>
+        <v>0.07249077703024216</v>
       </c>
       <c r="C12">
-        <v>25.08125263534662</v>
+        <v>24.8942053742364</v>
       </c>
       <c r="D12">
-        <v>16.06925263534662</v>
+        <v>16.1610053742364</v>
       </c>
       <c r="E12">
-        <v>-1.091999999999999</v>
+        <v>-0.8131999999999997</v>
       </c>
       <c r="F12">
-        <v>2.788</v>
+        <v>3.0668</v>
       </c>
       <c r="G12">
         <v>11.8</v>
@@ -2271,28 +2271,28 @@
         <v>2.42</v>
       </c>
       <c r="M12">
-        <v>0.1402364</v>
+        <v>0.15426004</v>
       </c>
       <c r="N12">
-        <v>2.2797636</v>
+        <v>2.26573996</v>
       </c>
       <c r="O12">
-        <v>0.68392908</v>
+        <v>0.6797219879999999</v>
       </c>
       <c r="P12">
-        <v>1.59583452</v>
+        <v>1.586017972</v>
       </c>
       <c r="Q12">
-        <v>4.005834520000001</v>
+        <v>3.996017972</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07684677320387785</v>
+        <v>0.07709851351712602</v>
       </c>
       <c r="T12">
-        <v>0.7170155474336686</v>
+        <v>0.7228294114809705</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.25657532566438</v>
+        <v>15.68779575060398</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07249077703024216</v>
+        <v>0.07229845817699425</v>
       </c>
       <c r="C13">
-        <v>24.8942053742364</v>
+        <v>24.70821191567958</v>
       </c>
       <c r="D13">
-        <v>16.1610053742364</v>
+        <v>16.25381191567958</v>
       </c>
       <c r="E13">
-        <v>-0.8131999999999997</v>
+        <v>-0.5343999999999998</v>
       </c>
       <c r="F13">
-        <v>3.0668</v>
+        <v>3.3456</v>
       </c>
       <c r="G13">
         <v>11.8</v>
@@ -2353,28 +2353,28 @@
         <v>2.42</v>
       </c>
       <c r="M13">
-        <v>0.15426004</v>
+        <v>0.16828368</v>
       </c>
       <c r="N13">
-        <v>2.26573996</v>
+        <v>2.25171632</v>
       </c>
       <c r="O13">
-        <v>0.6797219879999999</v>
+        <v>0.6755148959999999</v>
       </c>
       <c r="P13">
-        <v>1.586017972</v>
+        <v>1.576201424</v>
       </c>
       <c r="Q13">
-        <v>3.996017972</v>
+        <v>3.986201424</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07709851351712602</v>
+        <v>0.07735597520112983</v>
       </c>
       <c r="T13">
-        <v>0.7228294114809705</v>
+        <v>0.7287754088020746</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.68779575060398</v>
+        <v>14.38047943805365</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07229845817699425</v>
+        <v>0.07210613932374635</v>
       </c>
       <c r="C14">
-        <v>24.70821191567958</v>
+        <v>24.52329051930273</v>
       </c>
       <c r="D14">
-        <v>16.25381191567958</v>
+        <v>16.34769051930273</v>
       </c>
       <c r="E14">
-        <v>-0.5343999999999998</v>
+        <v>-0.2555999999999994</v>
       </c>
       <c r="F14">
-        <v>3.3456</v>
+        <v>3.6244</v>
       </c>
       <c r="G14">
         <v>11.8</v>
@@ -2435,28 +2435,28 @@
         <v>2.42</v>
       </c>
       <c r="M14">
-        <v>0.16828368</v>
+        <v>0.18230732</v>
       </c>
       <c r="N14">
-        <v>2.25171632</v>
+        <v>2.23769268</v>
       </c>
       <c r="O14">
-        <v>0.6755148959999999</v>
+        <v>0.6713078039999999</v>
       </c>
       <c r="P14">
-        <v>1.576201424</v>
+        <v>1.566384876</v>
       </c>
       <c r="Q14">
-        <v>3.986201424</v>
+        <v>3.976384876</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07735597520112983</v>
+        <v>0.07761935554453603</v>
       </c>
       <c r="T14">
-        <v>0.7287754088020746</v>
+        <v>0.7348580957167673</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.38047943805365</v>
+        <v>13.27428871204952</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07210613932374635</v>
+        <v>0.07206082047049843</v>
       </c>
       <c r="C15">
-        <v>24.52329051930273</v>
+        <v>24.2667705785444</v>
       </c>
       <c r="D15">
-        <v>16.34769051930273</v>
+        <v>16.3699705785444</v>
       </c>
       <c r="E15">
-        <v>-0.2555999999999994</v>
+        <v>0.023200000000001</v>
       </c>
       <c r="F15">
-        <v>3.6244</v>
+        <v>3.9032</v>
       </c>
       <c r="G15">
         <v>11.8</v>
@@ -2517,45 +2517,45 @@
         <v>2.42</v>
       </c>
       <c r="M15">
-        <v>0.18230732</v>
+        <v>0.20218576</v>
       </c>
       <c r="N15">
-        <v>2.23769268</v>
+        <v>2.21781424</v>
       </c>
       <c r="O15">
-        <v>0.6713078039999999</v>
+        <v>0.665344272</v>
       </c>
       <c r="P15">
-        <v>1.566384876</v>
+        <v>1.552469968</v>
       </c>
       <c r="Q15">
-        <v>3.976384876</v>
+        <v>3.962469968</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07761935554453603</v>
+        <v>0.07788886101220749</v>
       </c>
       <c r="T15">
-        <v>0.7348580957167673</v>
+        <v>0.7410822404666855</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.27428871204952</v>
+        <v>11.96919110425977</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07206082047049843</v>
+        <v>0.07187900161725053</v>
       </c>
       <c r="C16">
-        <v>24.2667705785444</v>
+        <v>24.07797192909575</v>
       </c>
       <c r="D16">
-        <v>16.3699705785444</v>
+        <v>16.45997192909574</v>
       </c>
       <c r="E16">
-        <v>0.023200000000001</v>
+        <v>0.3020000000000009</v>
       </c>
       <c r="F16">
-        <v>3.9032</v>
+        <v>4.182</v>
       </c>
       <c r="G16">
         <v>11.8</v>
@@ -2599,28 +2599,28 @@
         <v>2.42</v>
       </c>
       <c r="M16">
-        <v>0.20218576</v>
+        <v>0.2166276</v>
       </c>
       <c r="N16">
-        <v>2.21781424</v>
+        <v>2.2033724</v>
       </c>
       <c r="O16">
-        <v>0.665344272</v>
+        <v>0.66101172</v>
       </c>
       <c r="P16">
-        <v>1.552469968</v>
+        <v>1.54236068</v>
       </c>
       <c r="Q16">
-        <v>3.962469968</v>
+        <v>3.95236068</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07788886101220749</v>
+        <v>0.07816470778500062</v>
       </c>
       <c r="T16">
-        <v>0.7410822404666855</v>
+        <v>0.7474528356813076</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.96919110425977</v>
+        <v>11.17124503064245</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07187900161725053</v>
+        <v>0.07169718276400262</v>
       </c>
       <c r="C17">
-        <v>24.07797192909575</v>
+        <v>23.89016839738812</v>
       </c>
       <c r="D17">
-        <v>16.45997192909574</v>
+        <v>16.55096839738812</v>
       </c>
       <c r="E17">
-        <v>0.302</v>
+        <v>0.5808000000000004</v>
       </c>
       <c r="F17">
-        <v>4.181999999999999</v>
+        <v>4.4608</v>
       </c>
       <c r="G17">
         <v>11.8</v>
@@ -2681,28 +2681,28 @@
         <v>2.42</v>
       </c>
       <c r="M17">
-        <v>0.2166276</v>
+        <v>0.23106944</v>
       </c>
       <c r="N17">
-        <v>2.2033724</v>
+        <v>2.18893056</v>
       </c>
       <c r="O17">
-        <v>0.66101172</v>
+        <v>0.6566791679999999</v>
       </c>
       <c r="P17">
-        <v>1.54236068</v>
+        <v>1.532251392</v>
       </c>
       <c r="Q17">
-        <v>3.95236068</v>
+        <v>3.942251392</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07816470778500062</v>
+        <v>0.07844712233809836</v>
       </c>
       <c r="T17">
-        <v>0.7474528356813076</v>
+        <v>0.7539751117343731</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.17124503064245</v>
+        <v>10.4730422162273</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07169718276400262</v>
+        <v>0.07151536391075471</v>
       </c>
       <c r="C18">
-        <v>23.89016839738812</v>
+        <v>23.70337657924334</v>
       </c>
       <c r="D18">
-        <v>16.55096839738812</v>
+        <v>16.64297657924334</v>
       </c>
       <c r="E18">
-        <v>0.5808000000000004</v>
+        <v>0.8596000000000008</v>
       </c>
       <c r="F18">
-        <v>4.4608</v>
+        <v>4.7396</v>
       </c>
       <c r="G18">
         <v>11.8</v>
@@ -2763,28 +2763,28 @@
         <v>2.42</v>
       </c>
       <c r="M18">
-        <v>0.23106944</v>
+        <v>0.24551128</v>
       </c>
       <c r="N18">
-        <v>2.18893056</v>
+        <v>2.17448872</v>
       </c>
       <c r="O18">
-        <v>0.6566791679999999</v>
+        <v>0.6523466159999999</v>
       </c>
       <c r="P18">
-        <v>1.532251392</v>
+        <v>1.522142104</v>
       </c>
       <c r="Q18">
-        <v>3.942251392</v>
+        <v>3.932142104</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07844712233809836</v>
+        <v>0.07873634206115027</v>
       </c>
       <c r="T18">
-        <v>0.7539751117343731</v>
+        <v>0.7606545510658258</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.4730422162273</v>
+        <v>9.856980909390394</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07151536391075471</v>
+        <v>0.0715477450575068</v>
       </c>
       <c r="C19">
-        <v>23.70337657924334</v>
+        <v>23.40811552703909</v>
       </c>
       <c r="D19">
-        <v>16.64297657924334</v>
+        <v>16.62651552703909</v>
       </c>
       <c r="E19">
-        <v>0.8596000000000008</v>
+        <v>1.138400000000001</v>
       </c>
       <c r="F19">
-        <v>4.7396</v>
+        <v>5.018400000000001</v>
       </c>
       <c r="G19">
         <v>11.8</v>
@@ -2845,45 +2845,45 @@
         <v>2.42</v>
       </c>
       <c r="M19">
-        <v>0.24551128</v>
+        <v>0.2684844</v>
       </c>
       <c r="N19">
-        <v>2.17448872</v>
+        <v>2.1515156</v>
       </c>
       <c r="O19">
-        <v>0.6523466159999999</v>
+        <v>0.6454546799999999</v>
       </c>
       <c r="P19">
-        <v>1.522142104</v>
+        <v>1.50606092</v>
       </c>
       <c r="Q19">
-        <v>3.932142104</v>
+        <v>3.91606092</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07873634206115027</v>
+        <v>0.0790326159237888</v>
       </c>
       <c r="T19">
-        <v>0.7606545510658258</v>
+        <v>0.7674969035517041</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>9.856980909390394</v>
+        <v>9.013559074568205</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07154774505750681</v>
+        <v>0.07137782620425889</v>
       </c>
       <c r="C20">
-        <v>23.40811552703908</v>
+        <v>23.21605905441993</v>
       </c>
       <c r="D20">
-        <v>16.62651552703908</v>
+        <v>16.71325905441993</v>
       </c>
       <c r="E20">
-        <v>1.1384</v>
+        <v>1.417200000000001</v>
       </c>
       <c r="F20">
-        <v>5.0184</v>
+        <v>5.2972</v>
       </c>
       <c r="G20">
         <v>11.8</v>
@@ -2927,28 +2927,28 @@
         <v>2.42</v>
       </c>
       <c r="M20">
-        <v>0.2684844</v>
+        <v>0.2834002</v>
       </c>
       <c r="N20">
-        <v>2.1515156</v>
+        <v>2.1365998</v>
       </c>
       <c r="O20">
-        <v>0.6454546799999999</v>
+        <v>0.6409799399999999</v>
       </c>
       <c r="P20">
-        <v>1.50606092</v>
+        <v>1.49561986</v>
       </c>
       <c r="Q20">
-        <v>3.91606092</v>
+        <v>3.90561986</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0790326159237888</v>
+        <v>0.07933620519044308</v>
       </c>
       <c r="T20">
-        <v>0.7674969035517041</v>
+        <v>0.7745082030125423</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.013559074568207</v>
+        <v>8.539161228538301</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07137782620425889</v>
+        <v>0.071207907351011</v>
       </c>
       <c r="C21">
-        <v>23.21605905441993</v>
+        <v>23.02491244192974</v>
       </c>
       <c r="D21">
-        <v>16.71325905441993</v>
+        <v>16.80091244192974</v>
       </c>
       <c r="E21">
-        <v>1.417200000000001</v>
+        <v>1.696000000000001</v>
       </c>
       <c r="F21">
-        <v>5.2972</v>
+        <v>5.576000000000001</v>
       </c>
       <c r="G21">
         <v>11.8</v>
@@ -3009,28 +3009,28 @@
         <v>2.42</v>
       </c>
       <c r="M21">
-        <v>0.2834002</v>
+        <v>0.298316</v>
       </c>
       <c r="N21">
-        <v>2.1365998</v>
+        <v>2.121684</v>
       </c>
       <c r="O21">
-        <v>0.6409799399999999</v>
+        <v>0.6365052</v>
       </c>
       <c r="P21">
-        <v>1.49561986</v>
+        <v>1.4851788</v>
       </c>
       <c r="Q21">
-        <v>3.90561986</v>
+        <v>3.8951788</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07933620519044308</v>
+        <v>0.07964738418876374</v>
       </c>
       <c r="T21">
-        <v>0.7745082030125423</v>
+        <v>0.7816947849599016</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.539161228538301</v>
+        <v>8.112203167111385</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.071207907351011</v>
+        <v>0.07103798849776308</v>
       </c>
       <c r="C22">
-        <v>23.02491244192974</v>
+        <v>22.8346900804408</v>
       </c>
       <c r="D22">
-        <v>16.80091244192974</v>
+        <v>16.8894900804408</v>
       </c>
       <c r="E22">
-        <v>1.696000000000001</v>
+        <v>1.974800000000001</v>
       </c>
       <c r="F22">
-        <v>5.576000000000001</v>
+        <v>5.8548</v>
       </c>
       <c r="G22">
         <v>11.8</v>
@@ -3091,28 +3091,28 @@
         <v>2.42</v>
       </c>
       <c r="M22">
-        <v>0.298316</v>
+        <v>0.3132318</v>
       </c>
       <c r="N22">
-        <v>2.121684</v>
+        <v>2.1067682</v>
       </c>
       <c r="O22">
-        <v>0.6365052</v>
+        <v>0.63203046</v>
       </c>
       <c r="P22">
-        <v>1.4851788</v>
+        <v>1.47473774</v>
       </c>
       <c r="Q22">
-        <v>3.8951788</v>
+        <v>3.88473774</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07964738418876374</v>
+        <v>0.07996644113640897</v>
       </c>
       <c r="T22">
-        <v>0.7816947849599016</v>
+        <v>0.7890633056907383</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.112203167111385</v>
+        <v>7.725907778201319</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07103798849776308</v>
+        <v>0.07099126964451517</v>
       </c>
       <c r="C23">
-        <v>22.8346900804408</v>
+        <v>22.58040826859508</v>
       </c>
       <c r="D23">
-        <v>16.8894900804408</v>
+        <v>16.91400826859508</v>
       </c>
       <c r="E23">
-        <v>1.974800000000001</v>
+        <v>2.2536</v>
       </c>
       <c r="F23">
-        <v>5.8548</v>
+        <v>6.133599999999999</v>
       </c>
       <c r="G23">
         <v>11.8</v>
@@ -3173,45 +3173,45 @@
         <v>2.42</v>
       </c>
       <c r="M23">
-        <v>0.3132318</v>
+        <v>0.33305448</v>
       </c>
       <c r="N23">
-        <v>2.1067682</v>
+        <v>2.08694552</v>
       </c>
       <c r="O23">
-        <v>0.63203046</v>
+        <v>0.6260836559999999</v>
       </c>
       <c r="P23">
-        <v>1.47473774</v>
+        <v>1.460861864</v>
       </c>
       <c r="Q23">
-        <v>3.88473774</v>
+        <v>3.870861864</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07996644113640897</v>
+        <v>0.08029367903142971</v>
       </c>
       <c r="T23">
-        <v>0.7890633056907381</v>
+        <v>0.7966207628505707</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.725907778201319</v>
+        <v>7.26607851063886</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07099126964451517</v>
+        <v>0.07082695079126727</v>
       </c>
       <c r="C24">
-        <v>22.58040826859508</v>
+        <v>22.38841166398132</v>
       </c>
       <c r="D24">
-        <v>16.91400826859508</v>
+        <v>17.00081166398132</v>
       </c>
       <c r="E24">
-        <v>2.2536</v>
+        <v>2.5324</v>
       </c>
       <c r="F24">
-        <v>6.133599999999999</v>
+        <v>6.4124</v>
       </c>
       <c r="G24">
         <v>11.8</v>
@@ -3255,28 +3255,28 @@
         <v>2.42</v>
       </c>
       <c r="M24">
-        <v>0.33305448</v>
+        <v>0.34819332</v>
       </c>
       <c r="N24">
-        <v>2.08694552</v>
+        <v>2.07180668</v>
       </c>
       <c r="O24">
-        <v>0.6260836559999999</v>
+        <v>0.6215420039999999</v>
       </c>
       <c r="P24">
-        <v>1.460861864</v>
+        <v>1.450264676</v>
       </c>
       <c r="Q24">
-        <v>3.870861864</v>
+        <v>3.860264676</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08029367903142971</v>
+        <v>0.08062941661203542</v>
       </c>
       <c r="T24">
-        <v>0.7966207628505707</v>
+        <v>0.8043745175989703</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.26607851063886</v>
+        <v>6.950162053654562</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07082695079126727</v>
+        <v>0.07066263193801936</v>
       </c>
       <c r="C25">
-        <v>22.38841166398132</v>
+        <v>22.19731061267037</v>
       </c>
       <c r="D25">
-        <v>17.00081166398132</v>
+        <v>17.08851061267037</v>
       </c>
       <c r="E25">
-        <v>2.5324</v>
+        <v>2.811200000000001</v>
       </c>
       <c r="F25">
-        <v>6.4124</v>
+        <v>6.6912</v>
       </c>
       <c r="G25">
         <v>11.8</v>
@@ -3337,28 +3337,28 @@
         <v>2.42</v>
       </c>
       <c r="M25">
-        <v>0.34819332</v>
+        <v>0.36333216</v>
       </c>
       <c r="N25">
-        <v>2.07180668</v>
+        <v>2.05666784</v>
       </c>
       <c r="O25">
-        <v>0.6215420039999999</v>
+        <v>0.6170003519999999</v>
       </c>
       <c r="P25">
-        <v>1.450264676</v>
+        <v>1.439667488</v>
       </c>
       <c r="Q25">
-        <v>3.860264676</v>
+        <v>3.849667488</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08062941661203542</v>
+        <v>0.08097398939213074</v>
       </c>
       <c r="T25">
-        <v>0.8043745175989703</v>
+        <v>0.8123323185249594</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.950162053654562</v>
+        <v>6.660571968085621</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07066263193801936</v>
+        <v>0.07049831308477146</v>
       </c>
       <c r="C26">
-        <v>22.19731061267037</v>
+        <v>22.00711904570221</v>
       </c>
       <c r="D26">
-        <v>17.08851061267037</v>
+        <v>17.17711904570221</v>
       </c>
       <c r="E26">
-        <v>2.8112</v>
+        <v>3.09</v>
       </c>
       <c r="F26">
-        <v>6.691199999999999</v>
+        <v>6.97</v>
       </c>
       <c r="G26">
         <v>11.8</v>
@@ -3419,28 +3419,28 @@
         <v>2.42</v>
       </c>
       <c r="M26">
-        <v>0.36333216</v>
+        <v>0.378471</v>
       </c>
       <c r="N26">
-        <v>2.05666784</v>
+        <v>2.041529</v>
       </c>
       <c r="O26">
-        <v>0.6170003519999999</v>
+        <v>0.6124586999999999</v>
       </c>
       <c r="P26">
-        <v>1.439667488</v>
+        <v>1.4290703</v>
       </c>
       <c r="Q26">
-        <v>3.849667488</v>
+        <v>3.8390703</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08097398939213074</v>
+        <v>0.08132775077969528</v>
       </c>
       <c r="T26">
-        <v>0.8123323185249594</v>
+        <v>0.8205023274756414</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.660571968085621</v>
+        <v>6.394149089362196</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07049831308477146</v>
+        <v>0.07033399423152355</v>
       </c>
       <c r="C27">
-        <v>22.00711904570221</v>
+        <v>21.81785118456734</v>
       </c>
       <c r="D27">
-        <v>17.17711904570221</v>
+        <v>17.26665118456734</v>
       </c>
       <c r="E27">
-        <v>3.09</v>
+        <v>3.368800000000001</v>
       </c>
       <c r="F27">
-        <v>6.97</v>
+        <v>7.2488</v>
       </c>
       <c r="G27">
         <v>11.8</v>
@@ -3501,28 +3501,28 @@
         <v>2.42</v>
       </c>
       <c r="M27">
-        <v>0.378471</v>
+        <v>0.39360984</v>
       </c>
       <c r="N27">
-        <v>2.041529</v>
+        <v>2.02639016</v>
       </c>
       <c r="O27">
-        <v>0.6124586999999999</v>
+        <v>0.607917048</v>
       </c>
       <c r="P27">
-        <v>1.4290703</v>
+        <v>1.418473112</v>
       </c>
       <c r="Q27">
-        <v>3.8390703</v>
+        <v>3.828473112</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08132775077969528</v>
+        <v>0.08169107328584263</v>
       </c>
       <c r="T27">
-        <v>0.8205023274756414</v>
+        <v>0.8288931474790445</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.394149089362196</v>
+        <v>6.148220278232881</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07033399423152355</v>
+        <v>0.07035867537827564</v>
       </c>
       <c r="C28">
-        <v>21.81785118456734</v>
+        <v>21.52554368966571</v>
       </c>
       <c r="D28">
-        <v>17.26665118456734</v>
+        <v>17.25314368966571</v>
       </c>
       <c r="E28">
-        <v>3.368800000000001</v>
+        <v>3.647600000000001</v>
       </c>
       <c r="F28">
-        <v>7.2488</v>
+        <v>7.527600000000001</v>
       </c>
       <c r="G28">
         <v>11.8</v>
@@ -3583,45 +3583,45 @@
         <v>2.42</v>
       </c>
       <c r="M28">
-        <v>0.39360984</v>
+        <v>0.4162762800000001</v>
       </c>
       <c r="N28">
-        <v>2.02639016</v>
+        <v>2.00372372</v>
       </c>
       <c r="O28">
-        <v>0.607917048</v>
+        <v>0.601117116</v>
       </c>
       <c r="P28">
-        <v>1.418473112</v>
+        <v>1.402606604</v>
       </c>
       <c r="Q28">
-        <v>3.828473112</v>
+        <v>3.812606604</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08169107328584263</v>
+        <v>0.08206434983325431</v>
       </c>
       <c r="T28">
-        <v>0.8288931474790445</v>
+        <v>0.8375138529619931</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.148220278232881</v>
+        <v>5.813446781065689</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07035867537827564</v>
+        <v>0.07020135652502772</v>
       </c>
       <c r="C29">
-        <v>21.52554368966571</v>
+        <v>21.33320490421391</v>
       </c>
       <c r="D29">
-        <v>17.25314368966571</v>
+        <v>17.33960490421391</v>
       </c>
       <c r="E29">
-        <v>3.647600000000001</v>
+        <v>3.926400000000001</v>
       </c>
       <c r="F29">
-        <v>7.527600000000001</v>
+        <v>7.806400000000001</v>
       </c>
       <c r="G29">
         <v>11.8</v>
@@ -3665,28 +3665,28 @@
         <v>2.42</v>
       </c>
       <c r="M29">
-        <v>0.4162762800000001</v>
+        <v>0.4316939200000001</v>
       </c>
       <c r="N29">
-        <v>2.00372372</v>
+        <v>1.98830608</v>
       </c>
       <c r="O29">
-        <v>0.601117116</v>
+        <v>0.5964918239999999</v>
       </c>
       <c r="P29">
-        <v>1.402606604</v>
+        <v>1.391814256</v>
       </c>
       <c r="Q29">
-        <v>3.812606604</v>
+        <v>3.801814256</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08206434983325431</v>
+        <v>0.08244799517364962</v>
       </c>
       <c r="T29">
-        <v>0.8375138529619931</v>
+        <v>0.8463740224861345</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.813446781065689</v>
+        <v>5.605823681741914</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07020135652502772</v>
+        <v>0.07004403767177983</v>
       </c>
       <c r="C30">
-        <v>21.33320490421391</v>
+        <v>21.14173705484798</v>
       </c>
       <c r="D30">
-        <v>17.33960490421391</v>
+        <v>17.42693705484798</v>
       </c>
       <c r="E30">
-        <v>3.926400000000001</v>
+        <v>4.205200000000001</v>
       </c>
       <c r="F30">
-        <v>7.806400000000001</v>
+        <v>8.0852</v>
       </c>
       <c r="G30">
         <v>11.8</v>
@@ -3747,28 +3747,28 @@
         <v>2.42</v>
       </c>
       <c r="M30">
-        <v>0.4316939200000001</v>
+        <v>0.44711156</v>
       </c>
       <c r="N30">
-        <v>1.98830608</v>
+        <v>1.97288844</v>
       </c>
       <c r="O30">
-        <v>0.5964918239999999</v>
+        <v>0.5918665319999999</v>
       </c>
       <c r="P30">
-        <v>1.391814256</v>
+        <v>1.381021908</v>
       </c>
       <c r="Q30">
-        <v>3.801814256</v>
+        <v>3.791021908</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08244799517364962</v>
+        <v>0.08284244742504202</v>
       </c>
       <c r="T30">
-        <v>0.8463740224861345</v>
+        <v>0.8554837742503928</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.605823681741914</v>
+        <v>5.412519416854263</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07004403767177983</v>
+        <v>0.06988671881853191</v>
       </c>
       <c r="C31">
-        <v>21.14173705484798</v>
+        <v>20.95115336777688</v>
       </c>
       <c r="D31">
-        <v>17.42693705484798</v>
+        <v>17.51515336777688</v>
       </c>
       <c r="E31">
-        <v>4.2052</v>
+        <v>4.484</v>
       </c>
       <c r="F31">
-        <v>8.085199999999999</v>
+        <v>8.363999999999999</v>
       </c>
       <c r="G31">
         <v>11.8</v>
@@ -3829,28 +3829,28 @@
         <v>2.42</v>
       </c>
       <c r="M31">
-        <v>0.44711156</v>
+        <v>0.4625292</v>
       </c>
       <c r="N31">
-        <v>1.97288844</v>
+        <v>1.9574708</v>
       </c>
       <c r="O31">
-        <v>0.5918665319999999</v>
+        <v>0.5872412399999999</v>
       </c>
       <c r="P31">
-        <v>1.381021908</v>
+        <v>1.37022956</v>
       </c>
       <c r="Q31">
-        <v>3.791021908</v>
+        <v>3.78022956</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08284244742504202</v>
+        <v>0.08324816974075988</v>
       </c>
       <c r="T31">
-        <v>0.8554837742503928</v>
+        <v>0.8648538046364869</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.412519416854264</v>
+        <v>5.232102102959121</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06988671881853191</v>
+        <v>0.069729399965284</v>
       </c>
       <c r="C32">
-        <v>20.95115336777688</v>
+        <v>20.76146733837991</v>
       </c>
       <c r="D32">
-        <v>17.51515336777688</v>
+        <v>17.60426733837991</v>
       </c>
       <c r="E32">
-        <v>4.484</v>
+        <v>4.7628</v>
       </c>
       <c r="F32">
-        <v>8.363999999999999</v>
+        <v>8.642799999999999</v>
       </c>
       <c r="G32">
         <v>11.8</v>
@@ -3911,28 +3911,28 @@
         <v>2.42</v>
       </c>
       <c r="M32">
-        <v>0.4625292</v>
+        <v>0.47794684</v>
       </c>
       <c r="N32">
-        <v>1.9574708</v>
+        <v>1.94205316</v>
       </c>
       <c r="O32">
-        <v>0.5872412399999999</v>
+        <v>0.5826159479999999</v>
       </c>
       <c r="P32">
-        <v>1.37022956</v>
+        <v>1.359437212</v>
       </c>
       <c r="Q32">
-        <v>3.78022956</v>
+        <v>3.769437212</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08324816974075988</v>
+        <v>0.08366565212360001</v>
       </c>
       <c r="T32">
-        <v>0.8648538046364869</v>
+        <v>0.8744954301062358</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.232102102959121</v>
+        <v>5.063324615766891</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.069729399965284</v>
+        <v>0.06957208111203611</v>
       </c>
       <c r="C33">
-        <v>20.76146733837991</v>
+        <v>20.57269273808917</v>
       </c>
       <c r="D33">
-        <v>17.60426733837991</v>
+        <v>17.69429273808917</v>
       </c>
       <c r="E33">
-        <v>4.7628</v>
+        <v>5.041600000000001</v>
       </c>
       <c r="F33">
-        <v>8.642799999999999</v>
+        <v>8.9216</v>
       </c>
       <c r="G33">
         <v>11.8</v>
@@ -3993,28 +3993,28 @@
         <v>2.42</v>
       </c>
       <c r="M33">
-        <v>0.47794684</v>
+        <v>0.49336448</v>
       </c>
       <c r="N33">
-        <v>1.94205316</v>
+        <v>1.92663552</v>
       </c>
       <c r="O33">
-        <v>0.5826159479999999</v>
+        <v>0.577990656</v>
       </c>
       <c r="P33">
-        <v>1.359437212</v>
+        <v>1.348644864</v>
       </c>
       <c r="Q33">
-        <v>3.769437212</v>
+        <v>3.758644864</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08366565212360001</v>
+        <v>0.0840954134000531</v>
       </c>
       <c r="T33">
-        <v>0.8744954301062358</v>
+        <v>0.8844206327956834</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.063324615766891</v>
+        <v>4.905095721524177</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06957208111203611</v>
+        <v>0.06941476225878819</v>
       </c>
       <c r="C34">
-        <v>20.57269273808917</v>
+        <v>20.38484362148439</v>
       </c>
       <c r="D34">
-        <v>17.69429273808917</v>
+        <v>17.78524362148438</v>
       </c>
       <c r="E34">
-        <v>5.041600000000001</v>
+        <v>5.320400000000001</v>
       </c>
       <c r="F34">
-        <v>8.9216</v>
+        <v>9.2004</v>
       </c>
       <c r="G34">
         <v>11.8</v>
@@ -4075,28 +4075,28 @@
         <v>2.42</v>
       </c>
       <c r="M34">
-        <v>0.49336448</v>
+        <v>0.50878212</v>
       </c>
       <c r="N34">
-        <v>1.92663552</v>
+        <v>1.91121788</v>
       </c>
       <c r="O34">
-        <v>0.577990656</v>
+        <v>0.5733653639999999</v>
       </c>
       <c r="P34">
-        <v>1.348644864</v>
+        <v>1.337852516</v>
       </c>
       <c r="Q34">
-        <v>3.758644864</v>
+        <v>3.747852516</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0840954134000531</v>
+        <v>0.08453800337132567</v>
       </c>
       <c r="T34">
-        <v>0.8844206327956834</v>
+        <v>0.8946421101922787</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.905095721524177</v>
+        <v>4.756456457235565</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06941476225878819</v>
+        <v>0.06925744340554028</v>
       </c>
       <c r="C35">
-        <v>20.38484362148439</v>
+        <v>20.19793433360741</v>
       </c>
       <c r="D35">
-        <v>17.78524362148438</v>
+        <v>17.87713433360741</v>
       </c>
       <c r="E35">
-        <v>5.320400000000001</v>
+        <v>5.599200000000002</v>
       </c>
       <c r="F35">
-        <v>9.2004</v>
+        <v>9.479200000000001</v>
       </c>
       <c r="G35">
         <v>11.8</v>
@@ -4157,28 +4157,28 @@
         <v>2.42</v>
       </c>
       <c r="M35">
-        <v>0.50878212</v>
+        <v>0.52419976</v>
       </c>
       <c r="N35">
-        <v>1.91121788</v>
+        <v>1.89580024</v>
       </c>
       <c r="O35">
-        <v>0.5733653639999999</v>
+        <v>0.5687400719999999</v>
       </c>
       <c r="P35">
-        <v>1.337852516</v>
+        <v>1.327060168</v>
       </c>
       <c r="Q35">
-        <v>3.747852516</v>
+        <v>3.737060168</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08453800337132567</v>
+        <v>0.08499400515990953</v>
       </c>
       <c r="T35">
-        <v>0.8946421101922787</v>
+        <v>0.9051733293281645</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.756456457235565</v>
+        <v>4.616560679081577</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06925744340554028</v>
+        <v>0.06971262455229238</v>
       </c>
       <c r="C36">
-        <v>20.19793433360741</v>
+        <v>19.65582337787858</v>
       </c>
       <c r="D36">
-        <v>17.87713433360741</v>
+        <v>17.61382337787857</v>
       </c>
       <c r="E36">
-        <v>5.599200000000002</v>
+        <v>5.878000000000002</v>
       </c>
       <c r="F36">
-        <v>9.479200000000001</v>
+        <v>9.758000000000001</v>
       </c>
       <c r="G36">
         <v>11.8</v>
@@ -4239,45 +4239,45 @@
         <v>2.42</v>
       </c>
       <c r="M36">
-        <v>0.52419976</v>
+        <v>0.5640124000000001</v>
       </c>
       <c r="N36">
-        <v>1.89580024</v>
+        <v>1.8559876</v>
       </c>
       <c r="O36">
-        <v>0.5687400719999999</v>
+        <v>0.5567962799999999</v>
       </c>
       <c r="P36">
-        <v>1.327060168</v>
+        <v>1.29919132</v>
       </c>
       <c r="Q36">
-        <v>3.737060168</v>
+        <v>3.70919132</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08499400515990953</v>
+        <v>0.08546403777275752</v>
       </c>
       <c r="T36">
-        <v>0.9051733293281645</v>
+        <v>0.916028585975924</v>
       </c>
       <c r="U36">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.616560679081577</v>
+        <v>4.290685807616995</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06971262455229238</v>
+        <v>0.06957280569904446</v>
       </c>
       <c r="C37">
-        <v>19.65582337787858</v>
+        <v>19.45707598401602</v>
       </c>
       <c r="D37">
-        <v>17.61382337787857</v>
+        <v>17.69387598401602</v>
       </c>
       <c r="E37">
-        <v>5.878000000000002</v>
+        <v>6.156800000000002</v>
       </c>
       <c r="F37">
-        <v>9.758000000000001</v>
+        <v>10.0368</v>
       </c>
       <c r="G37">
         <v>11.8</v>
@@ -4321,28 +4321,28 @@
         <v>2.42</v>
       </c>
       <c r="M37">
-        <v>0.5640124000000001</v>
+        <v>0.5801270400000001</v>
       </c>
       <c r="N37">
-        <v>1.8559876</v>
+        <v>1.83987296</v>
       </c>
       <c r="O37">
-        <v>0.5567962799999999</v>
+        <v>0.5519618879999999</v>
       </c>
       <c r="P37">
-        <v>1.29919132</v>
+        <v>1.287911072</v>
       </c>
       <c r="Q37">
-        <v>3.70919132</v>
+        <v>3.697911072</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08546403777275752</v>
+        <v>0.08594875890475699</v>
       </c>
       <c r="T37">
-        <v>0.916028585975924</v>
+        <v>0.9272230693939258</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.290685807616995</v>
+        <v>4.171500090738745</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06957280569904448</v>
+        <v>0.06943298684579657</v>
       </c>
       <c r="C38">
-        <v>19.45707598401601</v>
+        <v>19.25905957036675</v>
       </c>
       <c r="D38">
-        <v>17.69387598401601</v>
+        <v>17.77465957036675</v>
       </c>
       <c r="E38">
-        <v>6.1568</v>
+        <v>6.435600000000001</v>
       </c>
       <c r="F38">
-        <v>10.0368</v>
+        <v>10.3156</v>
       </c>
       <c r="G38">
         <v>11.8</v>
@@ -4403,28 +4403,28 @@
         <v>2.42</v>
       </c>
       <c r="M38">
-        <v>0.58012704</v>
+        <v>0.59624168</v>
       </c>
       <c r="N38">
-        <v>1.83987296</v>
+        <v>1.82375832</v>
       </c>
       <c r="O38">
-        <v>0.5519618879999999</v>
+        <v>0.547127496</v>
       </c>
       <c r="P38">
-        <v>1.287911072</v>
+        <v>1.276630824</v>
       </c>
       <c r="Q38">
-        <v>3.697911072</v>
+        <v>3.686630824</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08594875890475699</v>
+        <v>0.0864488680092009</v>
       </c>
       <c r="T38">
-        <v>0.9272230693939258</v>
+        <v>0.9387729332378959</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.171500090738745</v>
+        <v>4.058756845043105</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06943298684579657</v>
+        <v>0.07022416799254864</v>
       </c>
       <c r="C39">
-        <v>19.25905957036675</v>
+        <v>18.53261422155464</v>
       </c>
       <c r="D39">
-        <v>17.77465957036675</v>
+        <v>17.32701422155464</v>
       </c>
       <c r="E39">
-        <v>6.435600000000001</v>
+        <v>6.714400000000001</v>
       </c>
       <c r="F39">
-        <v>10.3156</v>
+        <v>10.5944</v>
       </c>
       <c r="G39">
         <v>11.8</v>
@@ -4485,45 +4485,45 @@
         <v>2.42</v>
       </c>
       <c r="M39">
-        <v>0.59624168</v>
+        <v>0.64943672</v>
       </c>
       <c r="N39">
-        <v>1.82375832</v>
+        <v>1.77056328</v>
       </c>
       <c r="O39">
-        <v>0.547127496</v>
+        <v>0.531168984</v>
       </c>
       <c r="P39">
-        <v>1.276630824</v>
+        <v>1.239394296</v>
       </c>
       <c r="Q39">
-        <v>3.686630824</v>
+        <v>3.649394296</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0864488680092009</v>
+        <v>0.08696510966540105</v>
       </c>
       <c r="T39">
-        <v>0.9387729332378959</v>
+        <v>0.9506953733348974</v>
       </c>
       <c r="U39">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V39">
         <v>0.3</v>
       </c>
       <c r="W39">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.058756845043105</v>
+        <v>3.726306082600319</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07022416799254864</v>
+        <v>0.07010884913930075</v>
       </c>
       <c r="C40">
-        <v>18.53261422155464</v>
+        <v>18.31765203894508</v>
       </c>
       <c r="D40">
-        <v>17.32701422155464</v>
+        <v>17.39085203894508</v>
       </c>
       <c r="E40">
-        <v>6.714400000000001</v>
+        <v>6.993200000000002</v>
       </c>
       <c r="F40">
-        <v>10.5944</v>
+        <v>10.8732</v>
       </c>
       <c r="G40">
         <v>11.8</v>
@@ -4567,28 +4567,28 @@
         <v>2.42</v>
       </c>
       <c r="M40">
-        <v>0.64943672</v>
+        <v>0.66652716</v>
       </c>
       <c r="N40">
-        <v>1.77056328</v>
+        <v>1.75347284</v>
       </c>
       <c r="O40">
-        <v>0.531168984</v>
+        <v>0.526041852</v>
       </c>
       <c r="P40">
-        <v>1.239394296</v>
+        <v>1.227430988</v>
       </c>
       <c r="Q40">
-        <v>3.649394296</v>
+        <v>3.637430988</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08696510966540105</v>
+        <v>0.08749827727754222</v>
       </c>
       <c r="T40">
-        <v>0.9506953733348974</v>
+        <v>0.9630087131072105</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.726306082600319</v>
+        <v>3.630759772790054</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07010884913930075</v>
+        <v>0.06999353028605285</v>
       </c>
       <c r="C41">
-        <v>18.31765203894508</v>
+        <v>18.10316199041258</v>
       </c>
       <c r="D41">
-        <v>17.39085203894508</v>
+        <v>17.45516199041258</v>
       </c>
       <c r="E41">
-        <v>6.993200000000002</v>
+        <v>7.272000000000002</v>
       </c>
       <c r="F41">
-        <v>10.8732</v>
+        <v>11.152</v>
       </c>
       <c r="G41">
         <v>11.8</v>
@@ -4649,28 +4649,28 @@
         <v>2.42</v>
       </c>
       <c r="M41">
-        <v>0.66652716</v>
+        <v>0.6836176</v>
       </c>
       <c r="N41">
-        <v>1.75347284</v>
+        <v>1.7363824</v>
       </c>
       <c r="O41">
-        <v>0.526041852</v>
+        <v>0.5209147199999999</v>
       </c>
       <c r="P41">
-        <v>1.227430988</v>
+        <v>1.21546768</v>
       </c>
       <c r="Q41">
-        <v>3.637430988</v>
+        <v>3.62546768</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08749827727754222</v>
+        <v>0.08804921714342141</v>
       </c>
       <c r="T41">
-        <v>0.9630087131072105</v>
+        <v>0.9757324975386006</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.630759772790054</v>
+        <v>3.539990778470302</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06999353028605285</v>
+        <v>0.07068181143280494</v>
       </c>
       <c r="C42">
-        <v>18.10316199041258</v>
+        <v>17.44742767277019</v>
       </c>
       <c r="D42">
-        <v>17.45516199041258</v>
+        <v>17.07822767277019</v>
       </c>
       <c r="E42">
-        <v>7.272000000000002</v>
+        <v>7.550800000000001</v>
       </c>
       <c r="F42">
-        <v>11.152</v>
+        <v>11.4308</v>
       </c>
       <c r="G42">
         <v>11.8</v>
@@ -4731,45 +4731,45 @@
         <v>2.42</v>
       </c>
       <c r="M42">
-        <v>0.6836176</v>
+        <v>0.7327142800000001</v>
       </c>
       <c r="N42">
-        <v>1.7363824</v>
+        <v>1.68728572</v>
       </c>
       <c r="O42">
-        <v>0.5209147199999999</v>
+        <v>0.506185716</v>
       </c>
       <c r="P42">
-        <v>1.21546768</v>
+        <v>1.181100004</v>
       </c>
       <c r="Q42">
-        <v>3.62546768</v>
+        <v>3.591100004</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08804921714342141</v>
+        <v>0.08861883293695752</v>
       </c>
       <c r="T42">
-        <v>0.9757324975386006</v>
+        <v>0.9888875966964784</v>
       </c>
       <c r="U42">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V42">
         <v>0.3</v>
       </c>
       <c r="W42">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.539990778470302</v>
+        <v>3.302788093607238</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07068181143280494</v>
+        <v>0.07058609257955703</v>
       </c>
       <c r="C43">
-        <v>17.44742767277019</v>
+        <v>17.22007021358174</v>
       </c>
       <c r="D43">
-        <v>17.07822767277019</v>
+        <v>17.12967021358174</v>
       </c>
       <c r="E43">
-        <v>7.550800000000001</v>
+        <v>7.829600000000001</v>
       </c>
       <c r="F43">
-        <v>11.4308</v>
+        <v>11.7096</v>
       </c>
       <c r="G43">
         <v>11.8</v>
@@ -4813,28 +4813,28 @@
         <v>2.42</v>
       </c>
       <c r="M43">
-        <v>0.7327142800000001</v>
+        <v>0.7505853600000001</v>
       </c>
       <c r="N43">
-        <v>1.68728572</v>
+        <v>1.66941464</v>
       </c>
       <c r="O43">
-        <v>0.506185716</v>
+        <v>0.500824392</v>
       </c>
       <c r="P43">
-        <v>1.181100004</v>
+        <v>1.168590248</v>
       </c>
       <c r="Q43">
-        <v>3.591100004</v>
+        <v>3.578590248</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08861883293695752</v>
+        <v>0.08920809065440867</v>
       </c>
       <c r="T43">
-        <v>0.9888875966964784</v>
+        <v>1.002496319963249</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.302788093607238</v>
+        <v>3.224150281854684</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07058609257955703</v>
+        <v>0.07049037372630912</v>
       </c>
       <c r="C44">
-        <v>17.22007021358174</v>
+        <v>16.99302359815911</v>
       </c>
       <c r="D44">
-        <v>17.12967021358174</v>
+        <v>17.1814235981591</v>
       </c>
       <c r="E44">
-        <v>7.829600000000001</v>
+        <v>8.1084</v>
       </c>
       <c r="F44">
-        <v>11.7096</v>
+        <v>11.9884</v>
       </c>
       <c r="G44">
         <v>11.8</v>
@@ -4895,28 +4895,28 @@
         <v>2.42</v>
       </c>
       <c r="M44">
-        <v>0.7505853600000001</v>
+        <v>0.7684564399999999</v>
       </c>
       <c r="N44">
-        <v>1.66941464</v>
+        <v>1.65154356</v>
       </c>
       <c r="O44">
-        <v>0.500824392</v>
+        <v>0.495463068</v>
       </c>
       <c r="P44">
-        <v>1.168590248</v>
+        <v>1.156080492</v>
       </c>
       <c r="Q44">
-        <v>3.578590248</v>
+        <v>3.566080492</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08920809065440867</v>
+        <v>0.08981802408124406</v>
       </c>
       <c r="T44">
-        <v>1.002496319963249</v>
+        <v>1.016582542292011</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.224150281854684</v>
+        <v>3.149170042741785</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07049037372630912</v>
+        <v>0.07039465487306122</v>
       </c>
       <c r="C45">
-        <v>16.99302359815911</v>
+        <v>16.76629065247055</v>
       </c>
       <c r="D45">
-        <v>17.1814235981591</v>
+        <v>17.23349065247055</v>
       </c>
       <c r="E45">
-        <v>8.1084</v>
+        <v>8.3872</v>
       </c>
       <c r="F45">
-        <v>11.9884</v>
+        <v>12.2672</v>
       </c>
       <c r="G45">
         <v>11.8</v>
@@ -4977,28 +4977,28 @@
         <v>2.42</v>
       </c>
       <c r="M45">
-        <v>0.7684564399999999</v>
+        <v>0.7863275199999999</v>
       </c>
       <c r="N45">
-        <v>1.65154356</v>
+        <v>1.63367248</v>
       </c>
       <c r="O45">
-        <v>0.495463068</v>
+        <v>0.490101744</v>
       </c>
       <c r="P45">
-        <v>1.156080492</v>
+        <v>1.143570736</v>
       </c>
       <c r="Q45">
-        <v>3.566080492</v>
+        <v>3.553570736</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08981802408124406</v>
+        <v>0.09044974084475217</v>
       </c>
       <c r="T45">
-        <v>1.016582542292011</v>
+        <v>1.031171843989657</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.149170042741785</v>
+        <v>3.077597996315836</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07039465487306122</v>
+        <v>0.07029893601981331</v>
       </c>
       <c r="C46">
-        <v>16.76629065247055</v>
+        <v>16.53987423684403</v>
       </c>
       <c r="D46">
-        <v>17.23349065247055</v>
+        <v>17.28587423684403</v>
       </c>
       <c r="E46">
-        <v>8.3872</v>
+        <v>8.666</v>
       </c>
       <c r="F46">
-        <v>12.2672</v>
+        <v>12.546</v>
       </c>
       <c r="G46">
         <v>11.8</v>
@@ -5059,28 +5059,28 @@
         <v>2.42</v>
       </c>
       <c r="M46">
-        <v>0.7863275199999999</v>
+        <v>0.8041986</v>
       </c>
       <c r="N46">
-        <v>1.63367248</v>
+        <v>1.6158014</v>
       </c>
       <c r="O46">
-        <v>0.490101744</v>
+        <v>0.48474042</v>
       </c>
       <c r="P46">
-        <v>1.143570736</v>
+        <v>1.13106098</v>
       </c>
       <c r="Q46">
-        <v>3.553570736</v>
+        <v>3.54106098</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09044974084475217</v>
+        <v>0.09110442912693328</v>
       </c>
       <c r="T46">
-        <v>1.031171843989657</v>
+        <v>1.046291665749037</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.077597996315836</v>
+        <v>3.009206929731039</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07029893601981331</v>
+        <v>0.0727148171665654</v>
       </c>
       <c r="C47">
-        <v>16.53987423684403</v>
+        <v>15.02941883681911</v>
       </c>
       <c r="D47">
-        <v>17.28587423684403</v>
+        <v>16.05421883681911</v>
       </c>
       <c r="E47">
-        <v>8.666</v>
+        <v>8.944800000000001</v>
       </c>
       <c r="F47">
-        <v>12.546</v>
+        <v>12.8248</v>
       </c>
       <c r="G47">
         <v>11.8</v>
@@ -5141,45 +5141,45 @@
         <v>2.42</v>
       </c>
       <c r="M47">
-        <v>0.8041986</v>
+        <v>0.9221031200000001</v>
       </c>
       <c r="N47">
-        <v>1.6158014</v>
+        <v>1.49789688</v>
       </c>
       <c r="O47">
-        <v>0.48474042</v>
+        <v>0.4493690639999999</v>
       </c>
       <c r="P47">
-        <v>1.13106098</v>
+        <v>1.048527816</v>
       </c>
       <c r="Q47">
-        <v>3.54106098</v>
+        <v>3.458527816</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09110442912693328</v>
+        <v>0.09178336512326926</v>
       </c>
       <c r="T47">
-        <v>1.046291665749037</v>
+        <v>1.061971480906911</v>
       </c>
       <c r="U47">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V47">
         <v>0.3</v>
       </c>
       <c r="W47">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.009206929731039</v>
+        <v>2.624435323459267</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0727148171665654</v>
+        <v>0.07267369831331751</v>
       </c>
       <c r="C48">
-        <v>15.02941883681911</v>
+        <v>14.77011187238057</v>
       </c>
       <c r="D48">
-        <v>16.05421883681911</v>
+        <v>16.07371187238057</v>
       </c>
       <c r="E48">
-        <v>8.944800000000001</v>
+        <v>9.223600000000001</v>
       </c>
       <c r="F48">
-        <v>12.8248</v>
+        <v>13.1036</v>
       </c>
       <c r="G48">
         <v>11.8</v>
@@ -5223,28 +5223,28 @@
         <v>2.42</v>
       </c>
       <c r="M48">
-        <v>0.9221031200000001</v>
+        <v>0.9421488400000001</v>
       </c>
       <c r="N48">
-        <v>1.49789688</v>
+        <v>1.47785116</v>
       </c>
       <c r="O48">
-        <v>0.4493690639999999</v>
+        <v>0.4433553479999999</v>
       </c>
       <c r="P48">
-        <v>1.048527816</v>
+        <v>1.034495812</v>
       </c>
       <c r="Q48">
-        <v>3.458527816</v>
+        <v>3.444495812</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09178336512326926</v>
+        <v>0.09248792134588207</v>
       </c>
       <c r="T48">
-        <v>1.061971480906911</v>
+        <v>1.078242987202819</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.624435323459267</v>
+        <v>2.568596274023964</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07267369831331751</v>
+        <v>0.07263257946006958</v>
       </c>
       <c r="C49">
-        <v>14.77011187238057</v>
+        <v>14.51085230238334</v>
       </c>
       <c r="D49">
-        <v>16.07371187238057</v>
+        <v>16.09325230238334</v>
       </c>
       <c r="E49">
-        <v>9.223600000000001</v>
+        <v>9.502400000000002</v>
       </c>
       <c r="F49">
-        <v>13.1036</v>
+        <v>13.3824</v>
       </c>
       <c r="G49">
         <v>11.8</v>
@@ -5305,28 +5305,28 @@
         <v>2.42</v>
       </c>
       <c r="M49">
-        <v>0.9421488400000001</v>
+        <v>0.9621945600000001</v>
       </c>
       <c r="N49">
-        <v>1.47785116</v>
+        <v>1.45780544</v>
       </c>
       <c r="O49">
-        <v>0.4433553479999999</v>
+        <v>0.4373416319999999</v>
       </c>
       <c r="P49">
-        <v>1.034495812</v>
+        <v>1.020463808</v>
       </c>
       <c r="Q49">
-        <v>3.444495812</v>
+        <v>3.430463808</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09248792134588207</v>
+        <v>0.09321957588474919</v>
       </c>
       <c r="T49">
-        <v>1.078242987202819</v>
+        <v>1.095140320663954</v>
       </c>
       <c r="U49">
         <v>0.07190000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.568596274023964</v>
+        <v>2.515083851648464</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07263257946006958</v>
+        <v>0.07392916060682168</v>
       </c>
       <c r="C50">
-        <v>14.51085230238334</v>
+        <v>13.63791931355598</v>
       </c>
       <c r="D50">
-        <v>16.09325230238334</v>
+        <v>15.49911931355597</v>
       </c>
       <c r="E50">
-        <v>9.5024</v>
+        <v>9.7812</v>
       </c>
       <c r="F50">
-        <v>13.3824</v>
+        <v>13.6612</v>
       </c>
       <c r="G50">
         <v>11.8</v>
@@ -5387,45 +5387,45 @@
         <v>2.42</v>
       </c>
       <c r="M50">
-        <v>0.96219456</v>
+        <v>1.03551896</v>
       </c>
       <c r="N50">
-        <v>1.45780544</v>
+        <v>1.38448104</v>
       </c>
       <c r="O50">
-        <v>0.437341632</v>
+        <v>0.4153443119999999</v>
       </c>
       <c r="P50">
-        <v>1.020463808</v>
+        <v>0.9691367279999998</v>
       </c>
       <c r="Q50">
-        <v>3.430463808</v>
+        <v>3.379136728</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09321957588474919</v>
+        <v>0.09397992275847389</v>
       </c>
       <c r="T50">
-        <v>1.095140320663954</v>
+        <v>1.112700294652976</v>
       </c>
       <c r="U50">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.3</v>
       </c>
       <c r="W50">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.515083851648465</v>
+        <v>2.336992458351511</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07392916060682168</v>
+        <v>0.07391534175357377</v>
       </c>
       <c r="C51">
-        <v>13.63791931355598</v>
+        <v>13.36522015989427</v>
       </c>
       <c r="D51">
-        <v>15.49911931355597</v>
+        <v>15.50522015989427</v>
       </c>
       <c r="E51">
-        <v>9.7812</v>
+        <v>10.06</v>
       </c>
       <c r="F51">
-        <v>13.6612</v>
+        <v>13.94</v>
       </c>
       <c r="G51">
         <v>11.8</v>
@@ -5469,28 +5469,28 @@
         <v>2.42</v>
       </c>
       <c r="M51">
-        <v>1.03551896</v>
+        <v>1.056652</v>
       </c>
       <c r="N51">
-        <v>1.38448104</v>
+        <v>1.363348</v>
       </c>
       <c r="O51">
-        <v>0.4153443119999999</v>
+        <v>0.4090043999999999</v>
       </c>
       <c r="P51">
-        <v>0.9691367279999998</v>
+        <v>0.9543435999999998</v>
       </c>
       <c r="Q51">
-        <v>3.379136728</v>
+        <v>3.3643436</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09397992275847389</v>
+        <v>0.09477068350714754</v>
       </c>
       <c r="T51">
-        <v>1.112700294652976</v>
+        <v>1.13096266760156</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.336992458351511</v>
+        <v>2.29025260918448</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07391534175357377</v>
+        <v>0.07390152290032587</v>
       </c>
       <c r="C52">
-        <v>13.36522015989427</v>
+        <v>13.09252581101945</v>
       </c>
       <c r="D52">
-        <v>15.50522015989427</v>
+        <v>15.51132581101945</v>
       </c>
       <c r="E52">
-        <v>10.06</v>
+        <v>10.3388</v>
       </c>
       <c r="F52">
-        <v>13.94</v>
+        <v>14.2188</v>
       </c>
       <c r="G52">
         <v>11.8</v>
@@ -5551,28 +5551,28 @@
         <v>2.42</v>
       </c>
       <c r="M52">
-        <v>1.056652</v>
+        <v>1.07778504</v>
       </c>
       <c r="N52">
-        <v>1.363348</v>
+        <v>1.34221496</v>
       </c>
       <c r="O52">
-        <v>0.4090043999999999</v>
+        <v>0.402664488</v>
       </c>
       <c r="P52">
-        <v>0.9543435999999998</v>
+        <v>0.939550472</v>
       </c>
       <c r="Q52">
-        <v>3.3643436</v>
+        <v>3.349550472</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09477068350714754</v>
+        <v>0.09559372020474666</v>
       </c>
       <c r="T52">
-        <v>1.13096266760156</v>
+        <v>1.149970443527636</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.29025260918448</v>
+        <v>2.245345695278903</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07390152290032587</v>
+        <v>0.07388770404707795</v>
       </c>
       <c r="C53">
-        <v>13.09252581101945</v>
+        <v>12.81983627260986</v>
       </c>
       <c r="D53">
-        <v>15.51132581101945</v>
+        <v>15.51743627260986</v>
       </c>
       <c r="E53">
-        <v>10.3388</v>
+        <v>10.6176</v>
       </c>
       <c r="F53">
-        <v>14.2188</v>
+        <v>14.4976</v>
       </c>
       <c r="G53">
         <v>11.8</v>
@@ -5633,28 +5633,28 @@
         <v>2.42</v>
       </c>
       <c r="M53">
-        <v>1.07778504</v>
+        <v>1.09891808</v>
       </c>
       <c r="N53">
-        <v>1.34221496</v>
+        <v>1.32108192</v>
       </c>
       <c r="O53">
-        <v>0.402664488</v>
+        <v>0.396324576</v>
       </c>
       <c r="P53">
-        <v>0.939550472</v>
+        <v>0.9247573439999999</v>
       </c>
       <c r="Q53">
-        <v>3.349550472</v>
+        <v>3.334757344</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09559372020474666</v>
+        <v>0.09645105009807908</v>
       </c>
       <c r="T53">
-        <v>1.149970443527636</v>
+        <v>1.1697702101173</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.245345695278903</v>
+        <v>2.202165970369693</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07388770404707795</v>
+        <v>0.07387388519383005</v>
       </c>
       <c r="C54">
-        <v>12.81983627260986</v>
+        <v>12.54715155035277</v>
       </c>
       <c r="D54">
-        <v>15.51743627260986</v>
+        <v>15.52355155035277</v>
       </c>
       <c r="E54">
-        <v>10.6176</v>
+        <v>10.8964</v>
       </c>
       <c r="F54">
-        <v>14.4976</v>
+        <v>14.7764</v>
       </c>
       <c r="G54">
         <v>11.8</v>
@@ -5715,28 +5715,28 @@
         <v>2.42</v>
       </c>
       <c r="M54">
-        <v>1.09891808</v>
+        <v>1.12005112</v>
       </c>
       <c r="N54">
-        <v>1.32108192</v>
+        <v>1.29994888</v>
       </c>
       <c r="O54">
-        <v>0.396324576</v>
+        <v>0.3899846639999999</v>
       </c>
       <c r="P54">
-        <v>0.9247573439999999</v>
+        <v>0.9099642159999999</v>
       </c>
       <c r="Q54">
-        <v>3.334757344</v>
+        <v>3.319964216</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09645105009807908</v>
+        <v>0.09734486211453203</v>
       </c>
       <c r="T54">
-        <v>1.1697702101173</v>
+        <v>1.190412519966097</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.202165970369693</v>
+        <v>2.160615669041963</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07387388519383005</v>
+        <v>0.07386006634058215</v>
       </c>
       <c r="C55">
-        <v>12.54715155035277</v>
+        <v>12.27447164994442</v>
       </c>
       <c r="D55">
-        <v>15.52355155035277</v>
+        <v>15.52967164994442</v>
       </c>
       <c r="E55">
-        <v>10.8964</v>
+        <v>11.1752</v>
       </c>
       <c r="F55">
-        <v>14.7764</v>
+        <v>15.0552</v>
       </c>
       <c r="G55">
         <v>11.8</v>
@@ -5797,28 +5797,28 @@
         <v>2.42</v>
       </c>
       <c r="M55">
-        <v>1.12005112</v>
+        <v>1.14118416</v>
       </c>
       <c r="N55">
-        <v>1.29994888</v>
+        <v>1.27881584</v>
       </c>
       <c r="O55">
-        <v>0.3899846639999999</v>
+        <v>0.3836447519999999</v>
       </c>
       <c r="P55">
-        <v>0.9099642159999999</v>
+        <v>0.8951710879999999</v>
       </c>
       <c r="Q55">
-        <v>3.319964216</v>
+        <v>3.305171088</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09734486211453203</v>
+        <v>0.09827753552300465</v>
       </c>
       <c r="T55">
-        <v>1.190412519966097</v>
+        <v>1.211952321547451</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.160615669041963</v>
+        <v>2.120604267763408</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07386006634058215</v>
+        <v>0.07384624748733423</v>
       </c>
       <c r="C56">
-        <v>12.27447164994442</v>
+        <v>12.00179657709007</v>
       </c>
       <c r="D56">
-        <v>15.52967164994442</v>
+        <v>15.53579657709007</v>
       </c>
       <c r="E56">
-        <v>11.1752</v>
+        <v>11.454</v>
       </c>
       <c r="F56">
-        <v>15.0552</v>
+        <v>15.334</v>
       </c>
       <c r="G56">
         <v>11.8</v>
@@ -5879,28 +5879,28 @@
         <v>2.42</v>
       </c>
       <c r="M56">
-        <v>1.14118416</v>
+        <v>1.1623172</v>
       </c>
       <c r="N56">
-        <v>1.27881584</v>
+        <v>1.2576828</v>
       </c>
       <c r="O56">
-        <v>0.3836447519999999</v>
+        <v>0.3773048399999999</v>
       </c>
       <c r="P56">
-        <v>0.8951710879999999</v>
+        <v>0.8803779599999999</v>
       </c>
       <c r="Q56">
-        <v>3.305171088</v>
+        <v>3.29037796</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09827753552300465</v>
+        <v>0.09925166108296496</v>
       </c>
       <c r="T56">
-        <v>1.211952321547451</v>
+        <v>1.234449447643533</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.120604267763408</v>
+        <v>2.082047826531346</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07384624748733423</v>
+        <v>0.07383242863408633</v>
       </c>
       <c r="C57">
-        <v>12.00179657709007</v>
+        <v>11.72912633750393</v>
       </c>
       <c r="D57">
-        <v>15.53579657709007</v>
+        <v>15.54192633750393</v>
       </c>
       <c r="E57">
-        <v>11.454</v>
+        <v>11.7328</v>
       </c>
       <c r="F57">
-        <v>15.334</v>
+        <v>15.6128</v>
       </c>
       <c r="G57">
         <v>11.8</v>
@@ -5961,28 +5961,28 @@
         <v>2.42</v>
       </c>
       <c r="M57">
-        <v>1.1623172</v>
+        <v>1.18345024</v>
       </c>
       <c r="N57">
-        <v>1.2576828</v>
+        <v>1.23654976</v>
       </c>
       <c r="O57">
-        <v>0.3773048399999999</v>
+        <v>0.3709649279999999</v>
       </c>
       <c r="P57">
-        <v>0.8803779599999999</v>
+        <v>0.8655848319999998</v>
       </c>
       <c r="Q57">
-        <v>3.29037796</v>
+        <v>3.275584832</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09925166108296496</v>
+        <v>0.1002700650774689</v>
       </c>
       <c r="T57">
-        <v>1.234449447643533</v>
+        <v>1.257969170380345</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.082047826531346</v>
+        <v>2.044868401057572</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07383242863408633</v>
+        <v>0.07381860978083843</v>
       </c>
       <c r="C58">
-        <v>11.72912633750393</v>
+        <v>11.45646093690928</v>
       </c>
       <c r="D58">
-        <v>15.54192633750393</v>
+        <v>15.54806093690928</v>
       </c>
       <c r="E58">
-        <v>11.7328</v>
+        <v>12.0116</v>
       </c>
       <c r="F58">
-        <v>15.6128</v>
+        <v>15.8916</v>
       </c>
       <c r="G58">
         <v>11.8</v>
@@ -6043,28 +6043,28 @@
         <v>2.42</v>
       </c>
       <c r="M58">
-        <v>1.18345024</v>
+        <v>1.20458328</v>
       </c>
       <c r="N58">
-        <v>1.23654976</v>
+        <v>1.21541672</v>
       </c>
       <c r="O58">
-        <v>0.3709649279999999</v>
+        <v>0.364625016</v>
       </c>
       <c r="P58">
-        <v>0.8655848319999998</v>
+        <v>0.8507917039999999</v>
       </c>
       <c r="Q58">
-        <v>3.275584832</v>
+        <v>3.260791704</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1002700650774689</v>
+        <v>0.1013358366996242</v>
       </c>
       <c r="T58">
-        <v>1.257969170380345</v>
+        <v>1.282582833709566</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.044868401057572</v>
+        <v>2.008993516828492</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07381860978083843</v>
+        <v>0.07956999092759051</v>
       </c>
       <c r="C59">
-        <v>11.45646093690928</v>
+        <v>8.983842140064532</v>
       </c>
       <c r="D59">
-        <v>15.54806093690928</v>
+        <v>13.35424214006453</v>
       </c>
       <c r="E59">
-        <v>12.0116</v>
+        <v>12.2904</v>
       </c>
       <c r="F59">
-        <v>15.8916</v>
+        <v>16.1704</v>
       </c>
       <c r="G59">
         <v>11.8</v>
@@ -6125,45 +6125,45 @@
         <v>2.42</v>
       </c>
       <c r="M59">
-        <v>1.20458328</v>
+        <v>1.455336</v>
       </c>
       <c r="N59">
-        <v>1.21541672</v>
+        <v>0.964664</v>
       </c>
       <c r="O59">
-        <v>0.364625016</v>
+        <v>0.2893992</v>
       </c>
       <c r="P59">
-        <v>0.8507917039999999</v>
+        <v>0.6752648</v>
       </c>
       <c r="Q59">
-        <v>3.260791704</v>
+        <v>3.0852648</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1013358366996242</v>
+        <v>0.102452359351406</v>
       </c>
       <c r="T59">
-        <v>1.282582833709566</v>
+        <v>1.308368576244942</v>
       </c>
       <c r="U59">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V59">
         <v>0.3</v>
       </c>
       <c r="W59">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.008993516828492</v>
+        <v>1.662846243066893</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07956999092759051</v>
+        <v>0.0796555720743426</v>
       </c>
       <c r="C60">
-        <v>8.983842140064535</v>
+        <v>8.677062711409214</v>
       </c>
       <c r="D60">
-        <v>13.35424214006453</v>
+        <v>13.32626271140921</v>
       </c>
       <c r="E60">
-        <v>12.2904</v>
+        <v>12.5692</v>
       </c>
       <c r="F60">
-        <v>16.1704</v>
+        <v>16.4492</v>
       </c>
       <c r="G60">
         <v>11.8</v>
@@ -6207,28 +6207,28 @@
         <v>2.42</v>
       </c>
       <c r="M60">
-        <v>1.455336</v>
+        <v>1.480428</v>
       </c>
       <c r="N60">
-        <v>0.9646640000000002</v>
+        <v>0.9395720000000003</v>
       </c>
       <c r="O60">
-        <v>0.2893992</v>
+        <v>0.2818716000000001</v>
       </c>
       <c r="P60">
-        <v>0.6752648000000001</v>
+        <v>0.6577004000000002</v>
       </c>
       <c r="Q60">
-        <v>3.0852648</v>
+        <v>3.067700400000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.102452359351406</v>
+        <v>0.1036233465227868</v>
       </c>
       <c r="T60">
-        <v>1.308368576244942</v>
+        <v>1.335412159879603</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.662846243066893</v>
+        <v>1.634662408438641</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0796555720743426</v>
+        <v>0.07974115322109471</v>
       </c>
       <c r="C61">
-        <v>8.677062711409214</v>
+        <v>8.370400281030118</v>
       </c>
       <c r="D61">
-        <v>13.32626271140921</v>
+        <v>13.29840028103011</v>
       </c>
       <c r="E61">
-        <v>12.5692</v>
+        <v>12.848</v>
       </c>
       <c r="F61">
-        <v>16.4492</v>
+        <v>16.728</v>
       </c>
       <c r="G61">
         <v>11.8</v>
@@ -6289,28 +6289,28 @@
         <v>2.42</v>
       </c>
       <c r="M61">
-        <v>1.480428</v>
+        <v>1.50552</v>
       </c>
       <c r="N61">
-        <v>0.9395720000000003</v>
+        <v>0.9144800000000002</v>
       </c>
       <c r="O61">
-        <v>0.2818716000000001</v>
+        <v>0.274344</v>
       </c>
       <c r="P61">
-        <v>0.6577004000000002</v>
+        <v>0.6401360000000001</v>
       </c>
       <c r="Q61">
-        <v>3.067700400000001</v>
+        <v>3.050136</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1036233465227868</v>
+        <v>0.1048528830527367</v>
       </c>
       <c r="T61">
-        <v>1.335412159879603</v>
+        <v>1.363807922695998</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.634662408438641</v>
+        <v>1.607418034964664</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07974115322109471</v>
+        <v>0.07982673436784679</v>
       </c>
       <c r="C62">
-        <v>8.370400281030118</v>
+        <v>8.063854116601572</v>
       </c>
       <c r="D62">
-        <v>13.29840028103011</v>
+        <v>13.27065411660157</v>
       </c>
       <c r="E62">
-        <v>12.848</v>
+        <v>13.1268</v>
       </c>
       <c r="F62">
-        <v>16.728</v>
+        <v>17.0068</v>
       </c>
       <c r="G62">
         <v>11.8</v>
@@ -6371,28 +6371,28 @@
         <v>2.42</v>
       </c>
       <c r="M62">
-        <v>1.50552</v>
+        <v>1.530612</v>
       </c>
       <c r="N62">
-        <v>0.9144800000000002</v>
+        <v>0.8893880000000001</v>
       </c>
       <c r="O62">
-        <v>0.274344</v>
+        <v>0.2668164</v>
       </c>
       <c r="P62">
-        <v>0.6401360000000001</v>
+        <v>0.6225716000000001</v>
       </c>
       <c r="Q62">
-        <v>3.050136</v>
+        <v>3.0325716</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1048528830527367</v>
+        <v>0.1061454727380687</v>
       </c>
       <c r="T62">
-        <v>1.363807922695998</v>
+        <v>1.393659878477337</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.607418034964664</v>
+        <v>1.581066919637374</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07982673436784679</v>
+        <v>0.07991231551459888</v>
       </c>
       <c r="C63">
-        <v>8.063854116601572</v>
+        <v>7.75742349189693</v>
       </c>
       <c r="D63">
-        <v>13.27065411660157</v>
+        <v>13.24302349189693</v>
       </c>
       <c r="E63">
-        <v>13.1268</v>
+        <v>13.4056</v>
       </c>
       <c r="F63">
-        <v>17.0068</v>
+        <v>17.2856</v>
       </c>
       <c r="G63">
         <v>11.8</v>
@@ -6453,28 +6453,28 @@
         <v>2.42</v>
       </c>
       <c r="M63">
-        <v>1.530612</v>
+        <v>1.555704</v>
       </c>
       <c r="N63">
-        <v>0.8893880000000001</v>
+        <v>0.8642960000000002</v>
       </c>
       <c r="O63">
-        <v>0.2668164</v>
+        <v>0.2592888</v>
       </c>
       <c r="P63">
-        <v>0.6225716000000001</v>
+        <v>0.6050072000000002</v>
       </c>
       <c r="Q63">
-        <v>3.0325716</v>
+        <v>3.0150072</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1061454727380687</v>
+        <v>0.1075060934594707</v>
       </c>
       <c r="T63">
-        <v>1.393659878477337</v>
+        <v>1.425082989826114</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.581066919637374</v>
+        <v>1.555565840288384</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07991231551459888</v>
+        <v>0.07999789666135097</v>
       </c>
       <c r="C64">
-        <v>7.75742349189693</v>
+        <v>7.451107686725237</v>
       </c>
       <c r="D64">
-        <v>13.24302349189693</v>
+        <v>13.21550768672524</v>
       </c>
       <c r="E64">
-        <v>13.4056</v>
+        <v>13.6844</v>
       </c>
       <c r="F64">
-        <v>17.2856</v>
+        <v>17.5644</v>
       </c>
       <c r="G64">
         <v>11.8</v>
@@ -6535,28 +6535,28 @@
         <v>2.42</v>
       </c>
       <c r="M64">
-        <v>1.555704</v>
+        <v>1.580796</v>
       </c>
       <c r="N64">
-        <v>0.8642960000000002</v>
+        <v>0.8392040000000001</v>
       </c>
       <c r="O64">
-        <v>0.2592888</v>
+        <v>0.2517612</v>
       </c>
       <c r="P64">
-        <v>0.6050072000000002</v>
+        <v>0.5874428</v>
       </c>
       <c r="Q64">
-        <v>3.0150072</v>
+        <v>2.9974428</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1075060934594707</v>
+        <v>0.1089402612468945</v>
       </c>
       <c r="T64">
-        <v>1.425082989826114</v>
+        <v>1.458204647734284</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.555565840288384</v>
+        <v>1.530874319013965</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07999789666135097</v>
+        <v>0.08008347780810307</v>
       </c>
       <c r="C65">
-        <v>7.451107686725237</v>
+        <v>7.144905986868682</v>
       </c>
       <c r="D65">
-        <v>13.21550768672524</v>
+        <v>13.18810598686868</v>
       </c>
       <c r="E65">
-        <v>13.6844</v>
+        <v>13.9632</v>
       </c>
       <c r="F65">
-        <v>17.5644</v>
+        <v>17.8432</v>
       </c>
       <c r="G65">
         <v>11.8</v>
@@ -6617,28 +6617,28 @@
         <v>2.42</v>
       </c>
       <c r="M65">
-        <v>1.580796</v>
+        <v>1.605888</v>
       </c>
       <c r="N65">
-        <v>0.8392040000000001</v>
+        <v>0.8141119999999999</v>
       </c>
       <c r="O65">
-        <v>0.2517612</v>
+        <v>0.2442336</v>
       </c>
       <c r="P65">
-        <v>0.5874428</v>
+        <v>0.5698784</v>
       </c>
       <c r="Q65">
-        <v>2.9974428</v>
+        <v>2.9798784</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1089402612468945</v>
+        <v>0.1104541050225085</v>
       </c>
       <c r="T65">
-        <v>1.458204647734284</v>
+        <v>1.493166397748465</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.530874319013965</v>
+        <v>1.506954407779372</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08008347780810307</v>
+        <v>0.10910629885944</v>
       </c>
       <c r="C66">
-        <v>7.144905986868682</v>
+        <v>1.421308449622828</v>
       </c>
       <c r="D66">
-        <v>13.18810598686868</v>
+        <v>7.743308449622827</v>
       </c>
       <c r="E66">
-        <v>13.9632</v>
+        <v>14.242</v>
       </c>
       <c r="F66">
-        <v>17.8432</v>
+        <v>18.122</v>
       </c>
       <c r="G66">
         <v>11.8</v>
@@ -6699,45 +6699,45 @@
         <v>2.42</v>
       </c>
       <c r="M66">
-        <v>1.605888</v>
+        <v>2.6603096</v>
       </c>
       <c r="N66">
-        <v>0.8141119999999999</v>
+        <v>-0.2403096000000002</v>
       </c>
       <c r="O66">
-        <v>0.2442336</v>
+        <v>-0.07209288000000007</v>
       </c>
       <c r="P66">
-        <v>0.5698784</v>
+        <v>-0.1682167200000002</v>
       </c>
       <c r="Q66">
-        <v>2.9798784</v>
+        <v>2.24178328</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1104541050225085</v>
+        <v>0.1135042029310501</v>
       </c>
       <c r="T66">
-        <v>1.493166397748465</v>
+        <v>1.56360745799192</v>
       </c>
       <c r="U66">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.3</v>
+        <v>0.2729005676632524</v>
       </c>
       <c r="W66">
-        <v>0.063</v>
+        <v>0.1067381966670346</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.506954407779372</v>
+        <v>0.909668558877508</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.10910629885944</v>
+        <v>0.11011629885944</v>
       </c>
       <c r="C67">
-        <v>1.421308449622828</v>
+        <v>1.032832275655792</v>
       </c>
       <c r="D67">
-        <v>7.743308449622827</v>
+        <v>7.633632275655792</v>
       </c>
       <c r="E67">
-        <v>14.242</v>
+        <v>14.5208</v>
       </c>
       <c r="F67">
-        <v>18.122</v>
+        <v>18.4008</v>
       </c>
       <c r="G67">
         <v>11.8</v>
@@ -6781,37 +6781,37 @@
         <v>2.42</v>
       </c>
       <c r="M67">
-        <v>2.6603096</v>
+        <v>2.70123744</v>
       </c>
       <c r="N67">
-        <v>-0.2403096000000002</v>
+        <v>-0.2812374400000004</v>
       </c>
       <c r="O67">
-        <v>-0.07209288000000007</v>
+        <v>-0.08437123200000012</v>
       </c>
       <c r="P67">
-        <v>-0.1682167200000002</v>
+        <v>-0.1968662080000003</v>
       </c>
       <c r="Q67">
-        <v>2.24178328</v>
+        <v>2.213133792</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1135042029310501</v>
+        <v>0.1154955030172575</v>
       </c>
       <c r="T67">
-        <v>1.56360745799192</v>
+        <v>1.609595912638741</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2729005676632524</v>
+        <v>0.2687657105774455</v>
       </c>
       <c r="W67">
-        <v>0.1067381966670346</v>
+        <v>0.107345193687231</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.909668558877508</v>
+        <v>0.8958857019248184</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.11011629885944</v>
+        <v>0.11112629885944</v>
       </c>
       <c r="C68">
-        <v>1.032832275655792</v>
+        <v>0.6474196154259175</v>
       </c>
       <c r="D68">
-        <v>7.633632275655792</v>
+        <v>7.527019615425918</v>
       </c>
       <c r="E68">
-        <v>14.5208</v>
+        <v>14.7996</v>
       </c>
       <c r="F68">
-        <v>18.4008</v>
+        <v>18.6796</v>
       </c>
       <c r="G68">
         <v>11.8</v>
@@ -6863,37 +6863,37 @@
         <v>2.42</v>
       </c>
       <c r="M68">
-        <v>2.70123744</v>
+        <v>2.74216528</v>
       </c>
       <c r="N68">
-        <v>-0.2812374400000004</v>
+        <v>-0.3221652800000006</v>
       </c>
       <c r="O68">
-        <v>-0.08437123200000012</v>
+        <v>-0.09664958400000016</v>
       </c>
       <c r="P68">
-        <v>-0.1968662080000003</v>
+        <v>-0.2255156960000004</v>
       </c>
       <c r="Q68">
-        <v>2.213133792</v>
+        <v>2.184484304</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1154955030172575</v>
+        <v>0.1176074879571744</v>
       </c>
       <c r="T68">
-        <v>1.609595912638741</v>
+        <v>1.658371546355066</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2687657105774455</v>
+        <v>0.2647542820613643</v>
       </c>
       <c r="W68">
-        <v>0.107345193687231</v>
+        <v>0.1079340713933917</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8958857019248184</v>
+        <v>0.8825142735378808</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.11112629885944</v>
+        <v>0.11213629885944</v>
       </c>
       <c r="C69">
-        <v>0.6474196154259175</v>
+        <v>0.2649438801681718</v>
       </c>
       <c r="D69">
-        <v>7.527019615425918</v>
+        <v>7.423343880168173</v>
       </c>
       <c r="E69">
-        <v>14.7996</v>
+        <v>15.0784</v>
       </c>
       <c r="F69">
-        <v>18.6796</v>
+        <v>18.9584</v>
       </c>
       <c r="G69">
         <v>11.8</v>
@@ -6945,37 +6945,37 @@
         <v>2.42</v>
       </c>
       <c r="M69">
-        <v>2.74216528</v>
+        <v>2.78309312</v>
       </c>
       <c r="N69">
-        <v>-0.3221652800000006</v>
+        <v>-0.3630931200000003</v>
       </c>
       <c r="O69">
-        <v>-0.09664958400000016</v>
+        <v>-0.1089279360000001</v>
       </c>
       <c r="P69">
-        <v>-0.2255156960000004</v>
+        <v>-0.2541651840000002</v>
       </c>
       <c r="Q69">
-        <v>2.184484304</v>
+        <v>2.155834816</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1176074879571744</v>
+        <v>0.1198514719558361</v>
       </c>
       <c r="T69">
-        <v>1.658371546355066</v>
+        <v>1.710195657178662</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2647542820613643</v>
+        <v>0.2608608367369324</v>
       </c>
       <c r="W69">
-        <v>0.1079340713933917</v>
+        <v>0.1085056291670183</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8825142735378808</v>
+        <v>0.8695361224564415</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.11213629885944</v>
+        <v>0.11314629885944</v>
       </c>
       <c r="C70">
-        <v>0.2649438801681718</v>
+        <v>-0.1147146392036689</v>
       </c>
       <c r="D70">
-        <v>7.423343880168173</v>
+        <v>7.322485360796334</v>
       </c>
       <c r="E70">
-        <v>15.0784</v>
+        <v>15.3572</v>
       </c>
       <c r="F70">
-        <v>18.9584</v>
+        <v>19.2372</v>
       </c>
       <c r="G70">
         <v>11.8</v>
@@ -7027,37 +7027,37 @@
         <v>2.42</v>
       </c>
       <c r="M70">
-        <v>2.78309312</v>
+        <v>2.82402096</v>
       </c>
       <c r="N70">
-        <v>-0.3630931200000003</v>
+        <v>-0.4040209600000004</v>
       </c>
       <c r="O70">
-        <v>-0.1089279360000001</v>
+        <v>-0.1212062880000001</v>
       </c>
       <c r="P70">
-        <v>-0.2541651840000002</v>
+        <v>-0.2828146720000003</v>
       </c>
       <c r="Q70">
-        <v>2.155834816</v>
+        <v>2.127185328</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1198514719558361</v>
+        <v>0.1222402291157018</v>
       </c>
       <c r="T70">
-        <v>1.710195657178662</v>
+        <v>1.765363259023135</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2608608367369324</v>
+        <v>0.2570802449001653</v>
       </c>
       <c r="W70">
-        <v>0.1085056291670183</v>
+        <v>0.1090606200486558</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8695361224564415</v>
+        <v>0.8569341496672176</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.11314629885944</v>
+        <v>0.11415629885944</v>
       </c>
       <c r="C71">
-        <v>-0.1147146392036689</v>
+        <v>-0.491669233191864</v>
       </c>
       <c r="D71">
-        <v>7.322485360796334</v>
+        <v>7.224330766808137</v>
       </c>
       <c r="E71">
-        <v>15.3572</v>
+        <v>15.636</v>
       </c>
       <c r="F71">
-        <v>19.2372</v>
+        <v>19.516</v>
       </c>
       <c r="G71">
         <v>11.8</v>
@@ -7109,37 +7109,37 @@
         <v>2.42</v>
       </c>
       <c r="M71">
-        <v>2.82402096</v>
+        <v>2.864948800000001</v>
       </c>
       <c r="N71">
-        <v>-0.4040209600000004</v>
+        <v>-0.4449488000000006</v>
       </c>
       <c r="O71">
-        <v>-0.1212062880000001</v>
+        <v>-0.1334846400000002</v>
       </c>
       <c r="P71">
-        <v>-0.2828146720000003</v>
+        <v>-0.3114641600000004</v>
       </c>
       <c r="Q71">
-        <v>2.127185328</v>
+        <v>2.09853584</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1222402291157018</v>
+        <v>0.1247882367528918</v>
       </c>
       <c r="T71">
-        <v>1.765363259023135</v>
+        <v>1.824208700990573</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2570802449001653</v>
+        <v>0.2534076699730201</v>
       </c>
       <c r="W71">
-        <v>0.1090606200486558</v>
+        <v>0.1095997540479607</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8569341496672176</v>
+        <v>0.8446922332434001</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.11415629885944</v>
+        <v>0.11516629885944</v>
       </c>
       <c r="C72">
-        <v>-0.491669233191864</v>
+        <v>-0.8660271982155301</v>
       </c>
       <c r="D72">
-        <v>7.224330766808137</v>
+        <v>7.12877280178447</v>
       </c>
       <c r="E72">
-        <v>15.636</v>
+        <v>15.9148</v>
       </c>
       <c r="F72">
-        <v>19.516</v>
+        <v>19.7948</v>
       </c>
       <c r="G72">
         <v>11.8</v>
@@ -7191,37 +7191,37 @@
         <v>2.42</v>
       </c>
       <c r="M72">
-        <v>2.864948800000001</v>
+        <v>2.905876640000001</v>
       </c>
       <c r="N72">
-        <v>-0.4449488000000006</v>
+        <v>-0.4858766400000007</v>
       </c>
       <c r="O72">
-        <v>-0.1334846400000002</v>
+        <v>-0.1457629920000002</v>
       </c>
       <c r="P72">
-        <v>-0.3114641600000004</v>
+        <v>-0.3401136480000005</v>
       </c>
       <c r="Q72">
-        <v>2.09853584</v>
+        <v>2.069886352</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1247882367528918</v>
+        <v>0.1275119690547157</v>
       </c>
       <c r="T72">
-        <v>1.824208700990573</v>
+        <v>1.887112449300593</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2534076699730201</v>
+        <v>0.249838547860724</v>
       </c>
       <c r="W72">
-        <v>0.1095997540479607</v>
+        <v>0.1101237011740457</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8446922332434001</v>
+        <v>0.8327951595357466</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.11516629885944</v>
+        <v>0.11617629885944</v>
       </c>
       <c r="C73">
-        <v>-0.8660271982155265</v>
+        <v>-1.237890227861346</v>
       </c>
       <c r="D73">
-        <v>7.12877280178447</v>
+        <v>7.035709772138652</v>
       </c>
       <c r="E73">
-        <v>15.9148</v>
+        <v>16.1936</v>
       </c>
       <c r="F73">
-        <v>19.7948</v>
+        <v>20.0736</v>
       </c>
       <c r="G73">
         <v>11.8</v>
@@ -7273,37 +7273,37 @@
         <v>2.42</v>
       </c>
       <c r="M73">
-        <v>2.90587664</v>
+        <v>2.94680448</v>
       </c>
       <c r="N73">
-        <v>-0.4858766400000003</v>
+        <v>-0.52680448</v>
       </c>
       <c r="O73">
-        <v>-0.1457629920000001</v>
+        <v>-0.158041344</v>
       </c>
       <c r="P73">
-        <v>-0.3401136480000002</v>
+        <v>-0.368763136</v>
       </c>
       <c r="Q73">
-        <v>2.069886352</v>
+        <v>2.041236864</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1275119690547157</v>
+        <v>0.1304302536638126</v>
       </c>
       <c r="T73">
-        <v>1.887112449300592</v>
+        <v>1.954509322489899</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.249838547860724</v>
+        <v>0.2463685680293251</v>
       </c>
       <c r="W73">
-        <v>0.1101237011740457</v>
+        <v>0.1106330942132951</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8327951595357468</v>
+        <v>0.8212285600977504</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.11617629885944</v>
+        <v>0.11718629885944</v>
       </c>
       <c r="C74">
-        <v>-1.237890227861346</v>
+        <v>-1.607354773883607</v>
       </c>
       <c r="D74">
-        <v>7.035709772138652</v>
+        <v>6.945045226116392</v>
       </c>
       <c r="E74">
-        <v>16.1936</v>
+        <v>16.4724</v>
       </c>
       <c r="F74">
-        <v>20.0736</v>
+        <v>20.3524</v>
       </c>
       <c r="G74">
         <v>11.8</v>
@@ -7355,37 +7355,37 @@
         <v>2.42</v>
       </c>
       <c r="M74">
-        <v>2.94680448</v>
+        <v>2.98773232</v>
       </c>
       <c r="N74">
-        <v>-0.52680448</v>
+        <v>-0.5677323200000002</v>
       </c>
       <c r="O74">
-        <v>-0.158041344</v>
+        <v>-0.170319696</v>
       </c>
       <c r="P74">
-        <v>-0.368763136</v>
+        <v>-0.3974126240000001</v>
       </c>
       <c r="Q74">
-        <v>2.041236864</v>
+        <v>2.012587376</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1304302536638126</v>
+        <v>0.1335647075032131</v>
       </c>
       <c r="T74">
-        <v>1.954509322489899</v>
+        <v>2.026898556656191</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2463685680293251</v>
+        <v>0.2429936561385124</v>
       </c>
       <c r="W74">
-        <v>0.1106330942132951</v>
+        <v>0.1111285312788664</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8212285600977504</v>
+        <v>0.8099788537950414</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.11718629885944</v>
+        <v>0.1595304518627542</v>
       </c>
       <c r="C75">
-        <v>-1.607354773883607</v>
+        <v>-4.32218739949802</v>
       </c>
       <c r="D75">
-        <v>6.945045226116392</v>
+        <v>4.509012600501979</v>
       </c>
       <c r="E75">
-        <v>16.4724</v>
+        <v>16.7512</v>
       </c>
       <c r="F75">
-        <v>20.3524</v>
+        <v>20.6312</v>
       </c>
       <c r="G75">
         <v>11.8</v>
@@ -7437,45 +7437,45 @@
         <v>2.42</v>
       </c>
       <c r="M75">
-        <v>2.98773232</v>
+        <v>4.14274496</v>
       </c>
       <c r="N75">
-        <v>-0.5677323200000002</v>
+        <v>-1.72274496</v>
       </c>
       <c r="O75">
-        <v>-0.170319696</v>
+        <v>-0.516823488</v>
       </c>
       <c r="P75">
-        <v>-0.3974126240000001</v>
+        <v>-1.205921472</v>
       </c>
       <c r="Q75">
-        <v>2.012587376</v>
+        <v>1.204078528</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1335647075032131</v>
+        <v>0.1422254770353143</v>
       </c>
       <c r="T75">
-        <v>2.026898556656191</v>
+        <v>2.226916328760145</v>
       </c>
       <c r="U75">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.2429936561385124</v>
+        <v>0.1752461247336838</v>
       </c>
       <c r="W75">
-        <v>0.1111285312788664</v>
+        <v>0.1656105781534763</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.8099788537950414</v>
+        <v>0.5841537491122795</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1595304518627542</v>
+        <v>0.1610804518627542</v>
       </c>
       <c r="C76">
-        <v>-4.32218739949802</v>
+        <v>-4.658146727236002</v>
       </c>
       <c r="D76">
-        <v>4.509012600501979</v>
+        <v>4.451853272763997</v>
       </c>
       <c r="E76">
-        <v>16.7512</v>
+        <v>17.03</v>
       </c>
       <c r="F76">
-        <v>20.6312</v>
+        <v>20.91</v>
       </c>
       <c r="G76">
         <v>11.8</v>
@@ -7519,37 +7519,37 @@
         <v>2.42</v>
       </c>
       <c r="M76">
-        <v>4.14274496</v>
+        <v>4.198728</v>
       </c>
       <c r="N76">
-        <v>-1.72274496</v>
+        <v>-1.778728</v>
       </c>
       <c r="O76">
-        <v>-0.516823488</v>
+        <v>-0.5336184</v>
       </c>
       <c r="P76">
-        <v>-1.205921472</v>
+        <v>-1.2451096</v>
       </c>
       <c r="Q76">
-        <v>1.204078528</v>
+        <v>1.1648904</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1422254770353143</v>
+        <v>0.1460824961167269</v>
       </c>
       <c r="T76">
-        <v>2.226916328760145</v>
+        <v>2.315992981910551</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1752461247336838</v>
+        <v>0.1729095097372347</v>
       </c>
       <c r="W76">
-        <v>0.1656105781534763</v>
+        <v>0.1660797704447633</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5841537491122795</v>
+        <v>0.576365032457449</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1610804518627542</v>
+        <v>0.1626304518627542</v>
       </c>
       <c r="C77">
-        <v>-4.658146727236002</v>
+        <v>-4.992675014356678</v>
       </c>
       <c r="D77">
-        <v>4.451853272763997</v>
+        <v>4.396124985643322</v>
       </c>
       <c r="E77">
-        <v>17.03</v>
+        <v>17.3088</v>
       </c>
       <c r="F77">
-        <v>20.91</v>
+        <v>21.1888</v>
       </c>
       <c r="G77">
         <v>11.8</v>
@@ -7601,37 +7601,37 @@
         <v>2.42</v>
       </c>
       <c r="M77">
-        <v>4.198728</v>
+        <v>4.25471104</v>
       </c>
       <c r="N77">
-        <v>-1.778728</v>
+        <v>-1.83471104</v>
       </c>
       <c r="O77">
-        <v>-0.5336184</v>
+        <v>-0.550413312</v>
       </c>
       <c r="P77">
-        <v>-1.2451096</v>
+        <v>-1.284297728</v>
       </c>
       <c r="Q77">
-        <v>1.1648904</v>
+        <v>1.125702272</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1460824961167269</v>
+        <v>0.1502609334549238</v>
       </c>
       <c r="T77">
-        <v>2.315992981910551</v>
+        <v>2.412492689490157</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1729095097372347</v>
+        <v>0.1706343846091132</v>
       </c>
       <c r="W77">
-        <v>0.1660797704447633</v>
+        <v>0.1665366155704901</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.576365032457449</v>
+        <v>0.5687812820303773</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1626304518627542</v>
+        <v>0.1641804518627542</v>
       </c>
       <c r="C78">
-        <v>-4.992675014356678</v>
+        <v>-5.325825337731541</v>
       </c>
       <c r="D78">
-        <v>4.396124985643322</v>
+        <v>4.341774662268459</v>
       </c>
       <c r="E78">
-        <v>17.3088</v>
+        <v>17.5876</v>
       </c>
       <c r="F78">
-        <v>21.1888</v>
+        <v>21.4676</v>
       </c>
       <c r="G78">
         <v>11.8</v>
@@ -7683,37 +7683,37 @@
         <v>2.42</v>
       </c>
       <c r="M78">
-        <v>4.25471104</v>
+        <v>4.31069408</v>
       </c>
       <c r="N78">
-        <v>-1.83471104</v>
+        <v>-1.89069408</v>
       </c>
       <c r="O78">
-        <v>-0.550413312</v>
+        <v>-0.567208224</v>
       </c>
       <c r="P78">
-        <v>-1.284297728</v>
+        <v>-1.323485856</v>
       </c>
       <c r="Q78">
-        <v>1.125702272</v>
+        <v>1.086514144</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1502609334549238</v>
+        <v>0.1548027131703553</v>
       </c>
       <c r="T78">
-        <v>2.412492689490157</v>
+        <v>2.517383675989729</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1706343846091132</v>
+        <v>0.1684183536401637</v>
       </c>
       <c r="W78">
-        <v>0.1665366155704901</v>
+        <v>0.1669815945890551</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5687812820303773</v>
+        <v>0.5613945121338788</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1641804518627542</v>
+        <v>0.1657304518627542</v>
       </c>
       <c r="C79">
-        <v>-5.325825337731541</v>
+        <v>-5.657648181479694</v>
       </c>
       <c r="D79">
-        <v>4.341774662268459</v>
+        <v>4.288751818520306</v>
       </c>
       <c r="E79">
-        <v>17.5876</v>
+        <v>17.8664</v>
       </c>
       <c r="F79">
-        <v>21.4676</v>
+        <v>21.7464</v>
       </c>
       <c r="G79">
         <v>11.8</v>
@@ -7765,37 +7765,37 @@
         <v>2.42</v>
       </c>
       <c r="M79">
-        <v>4.31069408</v>
+        <v>4.36667712</v>
       </c>
       <c r="N79">
-        <v>-1.89069408</v>
+        <v>-1.94667712</v>
       </c>
       <c r="O79">
-        <v>-0.567208224</v>
+        <v>-0.5840031360000001</v>
       </c>
       <c r="P79">
-        <v>-1.323485856</v>
+        <v>-1.362673984</v>
       </c>
       <c r="Q79">
-        <v>1.086514144</v>
+        <v>1.047326016</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1548027131703553</v>
+        <v>0.159757381950826</v>
       </c>
       <c r="T79">
-        <v>2.517383675989729</v>
+        <v>2.631810206716535</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1684183536401637</v>
+        <v>0.1662591439781103</v>
       </c>
       <c r="W79">
-        <v>0.1669815945890551</v>
+        <v>0.1674151638891955</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5613945121338788</v>
+        <v>0.554197146593701</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1657304518627542</v>
+        <v>0.1672804518627542</v>
       </c>
       <c r="C80">
-        <v>-5.657648181479694</v>
+        <v>-5.988191593374484</v>
       </c>
       <c r="D80">
-        <v>4.288751818520306</v>
+        <v>4.237008406625518</v>
       </c>
       <c r="E80">
-        <v>17.8664</v>
+        <v>18.1452</v>
       </c>
       <c r="F80">
-        <v>21.7464</v>
+        <v>22.0252</v>
       </c>
       <c r="G80">
         <v>11.8</v>
@@ -7847,37 +7847,37 @@
         <v>2.42</v>
       </c>
       <c r="M80">
-        <v>4.36667712</v>
+        <v>4.42266016</v>
       </c>
       <c r="N80">
-        <v>-1.94667712</v>
+        <v>-2.00266016</v>
       </c>
       <c r="O80">
-        <v>-0.5840031360000001</v>
+        <v>-0.6007980480000001</v>
       </c>
       <c r="P80">
-        <v>-1.362673984</v>
+        <v>-1.401862112</v>
       </c>
       <c r="Q80">
-        <v>1.047326016</v>
+        <v>1.008137888</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.159757381950826</v>
+        <v>0.1651839239484844</v>
       </c>
       <c r="T80">
-        <v>2.631810206716535</v>
+        <v>2.757134502274466</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1662591439781103</v>
+        <v>0.1641545978518051</v>
       </c>
       <c r="W80">
-        <v>0.1674151638891955</v>
+        <v>0.1678377567513575</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.554197146593701</v>
+        <v>0.5471819928393502</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1672804518627542</v>
+        <v>0.1688304518627542</v>
       </c>
       <c r="C81">
-        <v>-5.988191593374484</v>
+        <v>-6.317501330062926</v>
       </c>
       <c r="D81">
-        <v>4.237008406625518</v>
+        <v>4.186498669937075</v>
       </c>
       <c r="E81">
-        <v>18.1452</v>
+        <v>18.424</v>
       </c>
       <c r="F81">
-        <v>22.0252</v>
+        <v>22.304</v>
       </c>
       <c r="G81">
         <v>11.8</v>
@@ -7929,37 +7929,37 @@
         <v>2.42</v>
       </c>
       <c r="M81">
-        <v>4.42266016</v>
+        <v>4.4786432</v>
       </c>
       <c r="N81">
-        <v>-2.00266016</v>
+        <v>-2.058643200000001</v>
       </c>
       <c r="O81">
-        <v>-0.6007980480000001</v>
+        <v>-0.6175929600000002</v>
       </c>
       <c r="P81">
-        <v>-1.401862112</v>
+        <v>-1.44105024</v>
       </c>
       <c r="Q81">
-        <v>1.008137888</v>
+        <v>0.9689497599999997</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1651839239484844</v>
+        <v>0.1711531201459086</v>
       </c>
       <c r="T81">
-        <v>2.757134502274466</v>
+        <v>2.894991227388189</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1641545978518051</v>
+        <v>0.1621026653786575</v>
       </c>
       <c r="W81">
-        <v>0.1678377567513575</v>
+        <v>0.1682497847919656</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5471819928393502</v>
+        <v>0.5403422179288584</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1688304518627542</v>
+        <v>0.1703804518627542</v>
       </c>
       <c r="C82">
-        <v>-6.317501330062926</v>
+        <v>-6.64562099202046</v>
       </c>
       <c r="D82">
-        <v>4.186498669937075</v>
+        <v>4.137179007979542</v>
       </c>
       <c r="E82">
-        <v>18.424</v>
+        <v>18.7028</v>
       </c>
       <c r="F82">
-        <v>22.304</v>
+        <v>22.5828</v>
       </c>
       <c r="G82">
         <v>11.8</v>
@@ -8011,37 +8011,37 @@
         <v>2.42</v>
       </c>
       <c r="M82">
-        <v>4.4786432</v>
+        <v>4.534626240000001</v>
       </c>
       <c r="N82">
-        <v>-2.058643200000001</v>
+        <v>-2.114626240000001</v>
       </c>
       <c r="O82">
-        <v>-0.6175929600000002</v>
+        <v>-0.6343878720000001</v>
       </c>
       <c r="P82">
-        <v>-1.44105024</v>
+        <v>-1.480238368000001</v>
       </c>
       <c r="Q82">
-        <v>0.9689497599999997</v>
+        <v>0.9297616319999995</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1711531201459086</v>
+        <v>0.177750652785167</v>
       </c>
       <c r="T82">
-        <v>2.894991227388189</v>
+        <v>3.04735918672441</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1621026653786575</v>
+        <v>0.1601013979048469</v>
       </c>
       <c r="W82">
-        <v>0.1682497847919656</v>
+        <v>0.1686516393007068</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5403422179288584</v>
+        <v>0.5336713263494898</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1703804518627542</v>
+        <v>0.1719304518627542</v>
       </c>
       <c r="C83">
-        <v>-6.64562099202046</v>
+        <v>-6.972592149077631</v>
       </c>
       <c r="D83">
-        <v>4.137179007979542</v>
+        <v>4.089007850922369</v>
       </c>
       <c r="E83">
-        <v>18.7028</v>
+        <v>18.9816</v>
       </c>
       <c r="F83">
-        <v>22.5828</v>
+        <v>22.8616</v>
       </c>
       <c r="G83">
         <v>11.8</v>
@@ -8093,37 +8093,37 @@
         <v>2.42</v>
       </c>
       <c r="M83">
-        <v>4.534626240000001</v>
+        <v>4.59060928</v>
       </c>
       <c r="N83">
-        <v>-2.114626240000001</v>
+        <v>-2.17060928</v>
       </c>
       <c r="O83">
-        <v>-0.6343878720000001</v>
+        <v>-0.651182784</v>
       </c>
       <c r="P83">
-        <v>-1.480238368000001</v>
+        <v>-1.519426496</v>
       </c>
       <c r="Q83">
-        <v>0.9297616319999995</v>
+        <v>0.8905735040000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.177750652785167</v>
+        <v>0.1850812446065651</v>
       </c>
       <c r="T83">
-        <v>3.04735918672441</v>
+        <v>3.216656919320211</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1601013979048469</v>
+        <v>0.1581489418328366</v>
       </c>
       <c r="W83">
-        <v>0.1686516393007068</v>
+        <v>0.1690436924799664</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5336713263494898</v>
+        <v>0.5271631394427887</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1719304518627542</v>
+        <v>0.1734804518627542</v>
       </c>
       <c r="C84">
-        <v>-6.972592149077631</v>
+        <v>-7.298454457278329</v>
       </c>
       <c r="D84">
-        <v>4.089007850922369</v>
+        <v>4.04194554272167</v>
       </c>
       <c r="E84">
-        <v>18.9816</v>
+        <v>19.2604</v>
       </c>
       <c r="F84">
-        <v>22.8616</v>
+        <v>23.1404</v>
       </c>
       <c r="G84">
         <v>11.8</v>
@@ -8175,37 +8175,37 @@
         <v>2.42</v>
       </c>
       <c r="M84">
-        <v>4.59060928</v>
+        <v>4.64659232</v>
       </c>
       <c r="N84">
-        <v>-2.17060928</v>
+        <v>-2.22659232</v>
       </c>
       <c r="O84">
-        <v>-0.651182784</v>
+        <v>-0.667977696</v>
       </c>
       <c r="P84">
-        <v>-1.519426496</v>
+        <v>-1.558614624</v>
       </c>
       <c r="Q84">
-        <v>0.8905735040000002</v>
+        <v>0.8513853760000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1850812446065651</v>
+        <v>0.1932742589951866</v>
       </c>
       <c r="T84">
-        <v>3.216656919320211</v>
+        <v>3.405872032221399</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1581489418328366</v>
+        <v>0.1562435328950916</v>
       </c>
       <c r="W84">
-        <v>0.1690436924799664</v>
+        <v>0.1694262985946656</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5271631394427887</v>
+        <v>0.520811776316972</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1734804518627542</v>
+        <v>0.1750304518627542</v>
       </c>
       <c r="C85">
-        <v>-7.298454457278329</v>
+        <v>-7.623245767759951</v>
       </c>
       <c r="D85">
-        <v>4.04194554272167</v>
+        <v>3.995954232240048</v>
       </c>
       <c r="E85">
-        <v>19.2604</v>
+        <v>19.5392</v>
       </c>
       <c r="F85">
-        <v>23.1404</v>
+        <v>23.4192</v>
       </c>
       <c r="G85">
         <v>11.8</v>
@@ -8257,37 +8257,37 @@
         <v>2.42</v>
       </c>
       <c r="M85">
-        <v>4.64659232</v>
+        <v>4.70257536</v>
       </c>
       <c r="N85">
-        <v>-2.22659232</v>
+        <v>-2.28257536</v>
       </c>
       <c r="O85">
-        <v>-0.667977696</v>
+        <v>-0.6847726079999999</v>
       </c>
       <c r="P85">
-        <v>-1.558614624</v>
+        <v>-1.597802752</v>
       </c>
       <c r="Q85">
-        <v>0.8513853760000001</v>
+        <v>0.8121972479999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1932742589951866</v>
+        <v>0.2024914001823858</v>
       </c>
       <c r="T85">
-        <v>3.405872032221399</v>
+        <v>3.618739034235238</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1562435328950916</v>
+        <v>0.1543834908368167</v>
       </c>
       <c r="W85">
-        <v>0.1694262985946656</v>
+        <v>0.1697997950399672</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.520811776316972</v>
+        <v>0.5146116361227223</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1750304518627542</v>
+        <v>0.1765804518627542</v>
       </c>
       <c r="C86">
-        <v>-7.623245767759951</v>
+        <v>-7.947002228283868</v>
       </c>
       <c r="D86">
-        <v>3.995954232240048</v>
+        <v>3.950997771716129</v>
       </c>
       <c r="E86">
-        <v>19.5392</v>
+        <v>19.818</v>
       </c>
       <c r="F86">
-        <v>23.4192</v>
+        <v>23.698</v>
       </c>
       <c r="G86">
         <v>11.8</v>
@@ -8339,37 +8339,37 @@
         <v>2.42</v>
       </c>
       <c r="M86">
-        <v>4.70257536</v>
+        <v>4.758558399999999</v>
       </c>
       <c r="N86">
-        <v>-2.28257536</v>
+        <v>-2.338558399999999</v>
       </c>
       <c r="O86">
-        <v>-0.6847726079999999</v>
+        <v>-0.7015675199999998</v>
       </c>
       <c r="P86">
-        <v>-1.597802752</v>
+        <v>-1.636990879999999</v>
       </c>
       <c r="Q86">
-        <v>0.8121972479999999</v>
+        <v>0.7730091200000007</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2024914001823857</v>
+        <v>0.2129374935278781</v>
       </c>
       <c r="T86">
-        <v>3.618739034235235</v>
+        <v>3.859988303184251</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1543834908368167</v>
+        <v>0.1525672144740306</v>
       </c>
       <c r="W86">
-        <v>0.1697997950399672</v>
+        <v>0.1701645033336147</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5146116361227223</v>
+        <v>0.5085573815801021</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1765804518627542</v>
+        <v>0.1781304518627542</v>
       </c>
       <c r="C87">
-        <v>-7.947002228283868</v>
+        <v>-8.269758377988516</v>
       </c>
       <c r="D87">
-        <v>3.950997771716129</v>
+        <v>3.907041622011481</v>
       </c>
       <c r="E87">
-        <v>19.818</v>
+        <v>20.0968</v>
       </c>
       <c r="F87">
-        <v>23.698</v>
+        <v>23.9768</v>
       </c>
       <c r="G87">
         <v>11.8</v>
@@ -8421,37 +8421,37 @@
         <v>2.42</v>
       </c>
       <c r="M87">
-        <v>4.758558399999999</v>
+        <v>4.814541439999999</v>
       </c>
       <c r="N87">
-        <v>-2.338558399999999</v>
+        <v>-2.394541439999999</v>
       </c>
       <c r="O87">
-        <v>-0.7015675199999998</v>
+        <v>-0.7183624319999998</v>
       </c>
       <c r="P87">
-        <v>-1.636990879999999</v>
+        <v>-1.676179008</v>
       </c>
       <c r="Q87">
-        <v>0.7730091200000007</v>
+        <v>0.7338209920000005</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2129374935278781</v>
+        <v>0.2248758859227265</v>
       </c>
       <c r="T87">
-        <v>3.859988303184251</v>
+        <v>4.135701753411698</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1525672144740306</v>
+        <v>0.1507931770964256</v>
       </c>
       <c r="W87">
-        <v>0.1701645033336147</v>
+        <v>0.1705207300390378</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5085573815801021</v>
+        <v>0.5026439236547522</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1781304518627542</v>
+        <v>0.2106849391975191</v>
       </c>
       <c r="C88">
-        <v>-8.269758377988516</v>
+        <v>-9.288577815228766</v>
       </c>
       <c r="D88">
-        <v>3.907041622011481</v>
+        <v>3.16702218477123</v>
       </c>
       <c r="E88">
-        <v>20.0968</v>
+        <v>20.3756</v>
       </c>
       <c r="F88">
-        <v>23.9768</v>
+        <v>24.2556</v>
       </c>
       <c r="G88">
         <v>11.8</v>
@@ -8503,45 +8503,45 @@
         <v>2.42</v>
       </c>
       <c r="M88">
-        <v>4.814541439999999</v>
+        <v>5.71947048</v>
       </c>
       <c r="N88">
-        <v>-2.394541439999999</v>
+        <v>-3.29947048</v>
       </c>
       <c r="O88">
-        <v>-0.7183624319999998</v>
+        <v>-0.989841144</v>
       </c>
       <c r="P88">
-        <v>-1.676179008</v>
+        <v>-2.309629336</v>
       </c>
       <c r="Q88">
-        <v>0.7338209920000005</v>
+        <v>0.1003706640000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2248758859227265</v>
+        <v>0.2429162412611277</v>
       </c>
       <c r="T88">
-        <v>4.135701753411698</v>
+        <v>4.552338135360916</v>
       </c>
       <c r="U88">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1507931770964256</v>
+        <v>0.12693482771503</v>
       </c>
       <c r="W88">
-        <v>0.1705207300390378</v>
+        <v>0.2058687676247959</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.5026439236547522</v>
+        <v>0.4231160923834334</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2106849391975191</v>
+        <v>0.2125849391975191</v>
       </c>
       <c r="C89">
-        <v>-9.288577815228766</v>
+        <v>-9.602004776615402</v>
       </c>
       <c r="D89">
-        <v>3.16702218477123</v>
+        <v>3.132395223384596</v>
       </c>
       <c r="E89">
-        <v>20.3756</v>
+        <v>20.6544</v>
       </c>
       <c r="F89">
-        <v>24.2556</v>
+        <v>24.5344</v>
       </c>
       <c r="G89">
         <v>11.8</v>
@@ -8585,37 +8585,37 @@
         <v>2.42</v>
       </c>
       <c r="M89">
-        <v>5.71947048</v>
+        <v>5.78521152</v>
       </c>
       <c r="N89">
-        <v>-3.29947048</v>
+        <v>-3.36521152</v>
       </c>
       <c r="O89">
-        <v>-0.989841144</v>
+        <v>-1.009563456</v>
       </c>
       <c r="P89">
-        <v>-2.309629336</v>
+        <v>-2.355648064</v>
       </c>
       <c r="Q89">
-        <v>0.1003706640000002</v>
+        <v>0.05435193600000021</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2429162412611277</v>
+        <v>0.259342594699555</v>
       </c>
       <c r="T89">
-        <v>4.552338135360916</v>
+        <v>4.931699646640993</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.12693482771503</v>
+        <v>0.1254923864909956</v>
       </c>
       <c r="W89">
-        <v>0.2058687676247959</v>
+        <v>0.2062088952654232</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4231160923834334</v>
+        <v>0.4183079549699853</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2125849391975191</v>
+        <v>0.2144849391975191</v>
       </c>
       <c r="C90">
-        <v>-9.602004776615402</v>
+        <v>-9.914682732473864</v>
       </c>
       <c r="D90">
-        <v>3.132395223384596</v>
+        <v>3.098517267526133</v>
       </c>
       <c r="E90">
-        <v>20.6544</v>
+        <v>20.9332</v>
       </c>
       <c r="F90">
-        <v>24.5344</v>
+        <v>24.8132</v>
       </c>
       <c r="G90">
         <v>11.8</v>
@@ -8667,37 +8667,37 @@
         <v>2.42</v>
       </c>
       <c r="M90">
-        <v>5.78521152</v>
+        <v>5.85095256</v>
       </c>
       <c r="N90">
-        <v>-3.36521152</v>
+        <v>-3.43095256</v>
       </c>
       <c r="O90">
-        <v>-1.009563456</v>
+        <v>-1.029285768</v>
       </c>
       <c r="P90">
-        <v>-2.355648064</v>
+        <v>-2.401666792</v>
       </c>
       <c r="Q90">
-        <v>0.05435193600000021</v>
+        <v>0.008333208000000258</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.259342594699555</v>
+        <v>0.2787555578540601</v>
       </c>
       <c r="T90">
-        <v>4.931699646640993</v>
+        <v>5.380035978153812</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1254923864909956</v>
+        <v>0.12408235967649</v>
       </c>
       <c r="W90">
-        <v>0.2062088952654232</v>
+        <v>0.2065413795882837</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4183079549699853</v>
+        <v>0.4136078655883001</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2144849391975191</v>
+        <v>0.2163849391975191</v>
       </c>
       <c r="C91">
-        <v>-9.914682732473864</v>
+        <v>-10.22663572505331</v>
       </c>
       <c r="D91">
-        <v>3.098517267526133</v>
+        <v>3.065364274946692</v>
       </c>
       <c r="E91">
-        <v>20.9332</v>
+        <v>21.212</v>
       </c>
       <c r="F91">
-        <v>24.8132</v>
+        <v>25.092</v>
       </c>
       <c r="G91">
         <v>11.8</v>
@@ -8749,37 +8749,37 @@
         <v>2.42</v>
       </c>
       <c r="M91">
-        <v>5.85095256</v>
+        <v>5.9166936</v>
       </c>
       <c r="N91">
-        <v>-3.43095256</v>
+        <v>-3.4966936</v>
       </c>
       <c r="O91">
-        <v>-1.029285768</v>
+        <v>-1.04900808</v>
       </c>
       <c r="P91">
-        <v>-2.401666792</v>
+        <v>-2.44768552</v>
       </c>
       <c r="Q91">
-        <v>0.008333208000000258</v>
+        <v>-0.03768552000000014</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2787555578540601</v>
+        <v>0.302051113639466</v>
       </c>
       <c r="T91">
-        <v>5.380035978153812</v>
+        <v>5.918039575969192</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.12408235967649</v>
+        <v>0.1227036667911957</v>
       </c>
       <c r="W91">
-        <v>0.2065413795882837</v>
+        <v>0.2068664753706361</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4136078655883001</v>
+        <v>0.4090122226373188</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2163849391975191</v>
+        <v>0.2182849391975191</v>
       </c>
       <c r="C92">
-        <v>-10.22663572505331</v>
+        <v>-10.53788677852315</v>
       </c>
       <c r="D92">
-        <v>3.065364274946692</v>
+        <v>3.032913221476852</v>
       </c>
       <c r="E92">
-        <v>21.212</v>
+        <v>21.4908</v>
       </c>
       <c r="F92">
-        <v>25.092</v>
+        <v>25.3708</v>
       </c>
       <c r="G92">
         <v>11.8</v>
@@ -8831,37 +8831,37 @@
         <v>2.42</v>
       </c>
       <c r="M92">
-        <v>5.9166936</v>
+        <v>5.98243464</v>
       </c>
       <c r="N92">
-        <v>-3.4966936</v>
+        <v>-3.56243464</v>
       </c>
       <c r="O92">
-        <v>-1.04900808</v>
+        <v>-1.068730392</v>
       </c>
       <c r="P92">
-        <v>-2.44768552</v>
+        <v>-2.493704248</v>
       </c>
       <c r="Q92">
-        <v>-0.03768552000000014</v>
+        <v>-0.08370424800000009</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.302051113639466</v>
+        <v>0.3305234595994068</v>
       </c>
       <c r="T92">
-        <v>5.918039575969192</v>
+        <v>6.575599528854659</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1227036667911957</v>
+        <v>0.1213552748484353</v>
       </c>
       <c r="W92">
-        <v>0.2068664753706361</v>
+        <v>0.207184426190739</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4090122226373188</v>
+        <v>0.4045175828281176</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2182849391975191</v>
+        <v>0.2201849391975191</v>
       </c>
       <c r="C93">
-        <v>-10.53788677852315</v>
+        <v>-10.84845795229736</v>
       </c>
       <c r="D93">
-        <v>3.032913221476852</v>
+        <v>3.001142047702643</v>
       </c>
       <c r="E93">
-        <v>21.4908</v>
+        <v>21.7696</v>
       </c>
       <c r="F93">
-        <v>25.3708</v>
+        <v>25.6496</v>
       </c>
       <c r="G93">
         <v>11.8</v>
@@ -8913,37 +8913,37 @@
         <v>2.42</v>
       </c>
       <c r="M93">
-        <v>5.98243464</v>
+        <v>6.04817568</v>
       </c>
       <c r="N93">
-        <v>-3.56243464</v>
+        <v>-3.62817568</v>
       </c>
       <c r="O93">
-        <v>-1.068730392</v>
+        <v>-1.088452704</v>
       </c>
       <c r="P93">
-        <v>-2.493704248</v>
+        <v>-2.539722976</v>
       </c>
       <c r="Q93">
-        <v>-0.08370424800000009</v>
+        <v>-0.129722976</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3305234595994068</v>
+        <v>0.3661138920493327</v>
       </c>
       <c r="T93">
-        <v>6.575599528854659</v>
+        <v>7.397549469961493</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1213552748484353</v>
+        <v>0.1200361957739958</v>
       </c>
       <c r="W93">
-        <v>0.207184426190739</v>
+        <v>0.2074954650364918</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4045175828281176</v>
+        <v>0.4001206525799859</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2201849391975191</v>
+        <v>0.2220849391975191</v>
       </c>
       <c r="C94">
-        <v>-10.84845795229736</v>
+        <v>-11.15837039104191</v>
       </c>
       <c r="D94">
-        <v>3.001142047702643</v>
+        <v>2.970029608958086</v>
       </c>
       <c r="E94">
-        <v>21.7696</v>
+        <v>22.0484</v>
       </c>
       <c r="F94">
-        <v>25.6496</v>
+        <v>25.9284</v>
       </c>
       <c r="G94">
         <v>11.8</v>
@@ -8995,37 +8995,37 @@
         <v>2.42</v>
       </c>
       <c r="M94">
-        <v>6.04817568</v>
+        <v>6.113916720000001</v>
       </c>
       <c r="N94">
-        <v>-3.62817568</v>
+        <v>-3.693916720000001</v>
       </c>
       <c r="O94">
-        <v>-1.088452704</v>
+        <v>-1.108175016</v>
       </c>
       <c r="P94">
-        <v>-2.539722976</v>
+        <v>-2.585741704000001</v>
       </c>
       <c r="Q94">
-        <v>-0.129722976</v>
+        <v>-0.1757417040000004</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3661138920493327</v>
+        <v>0.4118730194849516</v>
       </c>
       <c r="T94">
-        <v>7.397549469961493</v>
+        <v>8.454342251384563</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1200361957739958</v>
+        <v>0.1187454839914797</v>
       </c>
       <c r="W94">
-        <v>0.2074954650364918</v>
+        <v>0.2077998148748091</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4001206525799859</v>
+        <v>0.3958182799715989</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2220849391975191</v>
+        <v>0.2239849391975191</v>
       </c>
       <c r="C95">
-        <v>-11.15837039104191</v>
+        <v>-11.46764437160365</v>
       </c>
       <c r="D95">
-        <v>2.970029608958086</v>
+        <v>2.939555628396351</v>
       </c>
       <c r="E95">
-        <v>22.0484</v>
+        <v>22.3272</v>
       </c>
       <c r="F95">
-        <v>25.9284</v>
+        <v>26.2072</v>
       </c>
       <c r="G95">
         <v>11.8</v>
@@ -9077,37 +9077,37 @@
         <v>2.42</v>
       </c>
       <c r="M95">
-        <v>6.113916720000001</v>
+        <v>6.17965776</v>
       </c>
       <c r="N95">
-        <v>-3.693916720000001</v>
+        <v>-3.759657760000001</v>
       </c>
       <c r="O95">
-        <v>-1.108175016</v>
+        <v>-1.127897328</v>
       </c>
       <c r="P95">
-        <v>-2.585741704000001</v>
+        <v>-2.631760432</v>
       </c>
       <c r="Q95">
-        <v>-0.1757417040000004</v>
+        <v>-0.221760432</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4118730194849516</v>
+        <v>0.4728851893991104</v>
       </c>
       <c r="T95">
-        <v>8.454342251384563</v>
+        <v>9.863399293281994</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1187454839914797</v>
+        <v>0.1174822341617831</v>
       </c>
       <c r="W95">
-        <v>0.2077998148748091</v>
+        <v>0.2080976891846516</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3958182799715989</v>
+        <v>0.3916074472059436</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2239849391975191</v>
+        <v>0.2258849391975191</v>
       </c>
       <c r="C96">
-        <v>-11.46764437160365</v>
+        <v>-11.77629934707936</v>
       </c>
       <c r="D96">
-        <v>2.939555628396351</v>
+        <v>2.909700652920642</v>
       </c>
       <c r="E96">
-        <v>22.3272</v>
+        <v>22.606</v>
       </c>
       <c r="F96">
-        <v>26.2072</v>
+        <v>26.486</v>
       </c>
       <c r="G96">
         <v>11.8</v>
@@ -9159,37 +9159,37 @@
         <v>2.42</v>
       </c>
       <c r="M96">
-        <v>6.17965776</v>
+        <v>6.2453988</v>
       </c>
       <c r="N96">
-        <v>-3.759657760000001</v>
+        <v>-3.8253988</v>
       </c>
       <c r="O96">
-        <v>-1.127897328</v>
+        <v>-1.14761964</v>
       </c>
       <c r="P96">
-        <v>-2.631760432</v>
+        <v>-2.67777916</v>
       </c>
       <c r="Q96">
-        <v>-0.221760432</v>
+        <v>-0.2677791599999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4728851893991104</v>
+        <v>0.5583022272789328</v>
       </c>
       <c r="T96">
-        <v>9.863399293281994</v>
+        <v>11.8360791519384</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1174822341617831</v>
+        <v>0.1162455790653433</v>
       </c>
       <c r="W96">
-        <v>0.2080976891846516</v>
+        <v>0.2083892924563921</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3916074472059436</v>
+        <v>0.3874852635511442</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2258849391975191</v>
+        <v>0.2277849391975191</v>
       </c>
       <c r="C97">
-        <v>-11.77629934707936</v>
+        <v>-12.08435398822643</v>
       </c>
       <c r="D97">
-        <v>2.909700652920642</v>
+        <v>2.880446011773567</v>
       </c>
       <c r="E97">
-        <v>22.606</v>
+        <v>22.8848</v>
       </c>
       <c r="F97">
-        <v>26.486</v>
+        <v>26.7648</v>
       </c>
       <c r="G97">
         <v>11.8</v>
@@ -9241,37 +9241,37 @@
         <v>2.42</v>
       </c>
       <c r="M97">
-        <v>6.2453988</v>
+        <v>6.311139840000001</v>
       </c>
       <c r="N97">
-        <v>-3.8253988</v>
+        <v>-3.891139840000001</v>
       </c>
       <c r="O97">
-        <v>-1.14761964</v>
+        <v>-1.167341952</v>
       </c>
       <c r="P97">
-        <v>-2.67777916</v>
+        <v>-2.723797888000001</v>
       </c>
       <c r="Q97">
-        <v>-0.2677791599999999</v>
+        <v>-0.3137978880000007</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5583022272789328</v>
+        <v>0.6864277840986662</v>
       </c>
       <c r="T97">
-        <v>11.8360791519384</v>
+        <v>14.79509893992301</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1162455790653433</v>
+        <v>0.1150346876167459</v>
       </c>
       <c r="W97">
-        <v>0.2083892924563921</v>
+        <v>0.2086748206599713</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3874852635511442</v>
+        <v>0.3834489587224864</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.227784939197519</v>
+        <v>0.229684939197519</v>
       </c>
       <c r="C98">
-        <v>-12.08435398822643</v>
+        <v>-12.39182622240027</v>
       </c>
       <c r="D98">
-        <v>2.880446011773567</v>
+        <v>2.851773777599725</v>
       </c>
       <c r="E98">
-        <v>22.8848</v>
+        <v>23.1636</v>
       </c>
       <c r="F98">
-        <v>26.7648</v>
+        <v>27.0436</v>
       </c>
       <c r="G98">
         <v>11.8</v>
@@ -9323,37 +9323,37 @@
         <v>2.42</v>
       </c>
       <c r="M98">
-        <v>6.31113984</v>
+        <v>6.37688088</v>
       </c>
       <c r="N98">
-        <v>-3.89113984</v>
+        <v>-3.95688088</v>
       </c>
       <c r="O98">
-        <v>-1.167341952</v>
+        <v>-1.187064264</v>
       </c>
       <c r="P98">
-        <v>-2.723797888</v>
+        <v>-2.769816616</v>
       </c>
       <c r="Q98">
-        <v>-0.3137978879999999</v>
+        <v>-0.3598166159999998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6864277840986645</v>
+        <v>0.8999703787982193</v>
       </c>
       <c r="T98">
-        <v>14.79509893992297</v>
+        <v>19.72679858656396</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1150346876167459</v>
+        <v>0.1138487630021403</v>
       </c>
       <c r="W98">
-        <v>0.2086748206599713</v>
+        <v>0.2089544616840953</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3834489587224865</v>
+        <v>0.379495876673801</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.229684939197519</v>
+        <v>0.231584939197519</v>
       </c>
       <c r="C99">
-        <v>-12.39182622240027</v>
+        <v>-12.69873327018909</v>
       </c>
       <c r="D99">
-        <v>2.851773777599725</v>
+        <v>2.823666729810908</v>
       </c>
       <c r="E99">
-        <v>23.1636</v>
+        <v>23.4424</v>
       </c>
       <c r="F99">
-        <v>27.0436</v>
+        <v>27.3224</v>
       </c>
       <c r="G99">
         <v>11.8</v>
@@ -9405,37 +9405,37 @@
         <v>2.42</v>
       </c>
       <c r="M99">
-        <v>6.37688088</v>
+        <v>6.44262192</v>
       </c>
       <c r="N99">
-        <v>-3.95688088</v>
+        <v>-4.02262192</v>
       </c>
       <c r="O99">
-        <v>-1.187064264</v>
+        <v>-1.206786576</v>
       </c>
       <c r="P99">
-        <v>-2.769816616</v>
+        <v>-2.815835344</v>
       </c>
       <c r="Q99">
-        <v>-0.3598166159999998</v>
+        <v>-0.4058353439999998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8999703787982193</v>
+        <v>1.327055568197329</v>
       </c>
       <c r="T99">
-        <v>19.72679858656396</v>
+        <v>29.59019787984593</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1138487630021403</v>
+        <v>0.1126870409306899</v>
       </c>
       <c r="W99">
-        <v>0.2089544616840953</v>
+        <v>0.2092283957485433</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.379495876673801</v>
+        <v>0.3756234697689663</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.231584939197519</v>
+        <v>0.2334849391975191</v>
       </c>
       <c r="C100">
-        <v>-12.69873327018909</v>
+        <v>-13.00509167990341</v>
       </c>
       <c r="D100">
-        <v>2.823666729810908</v>
+        <v>2.796108320096584</v>
       </c>
       <c r="E100">
-        <v>23.4424</v>
+        <v>23.7212</v>
       </c>
       <c r="F100">
-        <v>27.3224</v>
+        <v>27.6012</v>
       </c>
       <c r="G100">
         <v>11.8</v>
@@ -9487,37 +9487,37 @@
         <v>2.42</v>
       </c>
       <c r="M100">
-        <v>6.44262192</v>
+        <v>6.50836296</v>
       </c>
       <c r="N100">
-        <v>-4.02262192</v>
+        <v>-4.08836296</v>
       </c>
       <c r="O100">
-        <v>-1.206786576</v>
+        <v>-1.226508888</v>
       </c>
       <c r="P100">
-        <v>-2.815835344</v>
+        <v>-2.861854072</v>
       </c>
       <c r="Q100">
-        <v>-0.4058353439999998</v>
+        <v>-0.4518540720000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.327055568197329</v>
+        <v>2.608311136394658</v>
       </c>
       <c r="T100">
-        <v>29.59019787984593</v>
+        <v>59.18039575969186</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1126870409306899</v>
+        <v>0.1115487879919961</v>
       </c>
       <c r="W100">
-        <v>0.2092283957485433</v>
+        <v>0.2094967957914873</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3756234697689663</v>
+        <v>0.3718292933066535</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2334849391975191</v>
-      </c>
-      <c r="C101">
-        <v>-13.00509167990341</v>
-      </c>
-      <c r="D101">
-        <v>2.796108320096584</v>
-      </c>
-      <c r="E101">
-        <v>23.7212</v>
-      </c>
-      <c r="F101">
-        <v>27.6012</v>
-      </c>
-      <c r="G101">
-        <v>11.8</v>
-      </c>
-      <c r="H101">
-        <v>24</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.83</v>
-      </c>
-      <c r="K101">
-        <v>2.41</v>
-      </c>
-      <c r="L101">
-        <v>2.42</v>
-      </c>
-      <c r="M101">
-        <v>6.50836296</v>
-      </c>
-      <c r="N101">
-        <v>-4.08836296</v>
-      </c>
-      <c r="O101">
-        <v>-1.226508888</v>
-      </c>
-      <c r="P101">
-        <v>-2.861854072</v>
-      </c>
-      <c r="Q101">
-        <v>-0.4518540720000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.608311136394658</v>
-      </c>
-      <c r="T101">
-        <v>59.18039575969186</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1115487879919961</v>
-      </c>
-      <c r="W101">
-        <v>0.2094967957914873</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3718292933066535</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
